--- a/artfynd/A 31237-2026 artfynd.xlsx
+++ b/artfynd/A 31237-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026757</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026786</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026787</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026789</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026790</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026791</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026782</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026784</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026760</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,6 +1693,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026767</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1740,6 +1795,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026771</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,8 +1897,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026772</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31237-2026 artfynd.xlsx
+++ b/artfynd/A 31237-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113026757</v>
+        <v>135890448</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>97511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476964</v>
+        <v>476945</v>
       </c>
       <c r="R2" t="n">
-        <v>7044485</v>
+        <v>7044429</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026757</t>
+          <t>https://artportalen.se/Sighting/135890448</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113026786</v>
+        <v>135890254</v>
       </c>
       <c r="B3" t="n">
-        <v>83173</v>
+        <v>92319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476664</v>
+        <v>476919</v>
       </c>
       <c r="R3" t="n">
-        <v>7044378</v>
+        <v>7044428</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +887,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026786</t>
+          <t>https://artportalen.se/Sighting/135890254</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113026787</v>
+        <v>135888100</v>
       </c>
       <c r="B4" t="n">
-        <v>83173</v>
+        <v>92044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476701</v>
+        <v>476816</v>
       </c>
       <c r="R4" t="n">
-        <v>7044398</v>
+        <v>7044593</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +999,27 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026787</t>
+          <t>https://artportalen.se/Sighting/135888100</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113026789</v>
+        <v>113026757</v>
       </c>
       <c r="B5" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476725</v>
+        <v>476964</v>
       </c>
       <c r="R5" t="n">
-        <v>7044414</v>
+        <v>7044485</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1082,16 +1112,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026789</t>
+          <t>https://artportalen.se/Sighting/113026757</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113026790</v>
+        <v>135888945</v>
       </c>
       <c r="B6" t="n">
-        <v>83173</v>
+        <v>92048</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1129,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476704</v>
+        <v>476754</v>
       </c>
       <c r="R6" t="n">
-        <v>7044407</v>
+        <v>7044651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1183,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,27 +1213,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026790</t>
+          <t>https://artportalen.se/Sighting/135888945</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113026791</v>
+        <v>135889310</v>
       </c>
       <c r="B7" t="n">
-        <v>83173</v>
+        <v>92048</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,34 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476694</v>
+        <v>476783</v>
       </c>
       <c r="R7" t="n">
-        <v>7044369</v>
+        <v>7044546</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1295,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1269,69 +1319,68 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026791</t>
+          <t>https://artportalen.se/Sighting/135889310</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113026782</v>
+        <v>135890261</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>92048</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476664</v>
+        <v>476916</v>
       </c>
       <c r="R8" t="n">
-        <v>7044374</v>
+        <v>7044435</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,12 +1407,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1378,62 +1437,62 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026782</t>
+          <t>https://artportalen.se/Sighting/135890261</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113026784</v>
+        <v>135890410</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>92048</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476748</v>
+        <v>476916</v>
       </c>
       <c r="R9" t="n">
-        <v>7044445</v>
+        <v>7044438</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1460,12 +1519,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1480,62 +1549,62 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026784</t>
+          <t>https://artportalen.se/Sighting/135890410</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113026760</v>
+        <v>135890469</v>
       </c>
       <c r="B10" t="n">
-        <v>80461</v>
+        <v>92048</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476908</v>
+        <v>476934</v>
       </c>
       <c r="R10" t="n">
-        <v>7044403</v>
+        <v>7044411</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,12 +1631,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1582,49 +1661,49 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026760</t>
+          <t>https://artportalen.se/Sighting/135890469</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113026767</v>
+        <v>113026786</v>
       </c>
       <c r="B11" t="n">
-        <v>97983</v>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1713,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476711</v>
+        <v>476664</v>
       </c>
       <c r="R11" t="n">
-        <v>7044397</v>
+        <v>7044378</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,38 +1774,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026767</t>
+          <t>https://artportalen.se/Sighting/113026786</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113026771</v>
+        <v>113026787</v>
       </c>
       <c r="B12" t="n">
-        <v>97983</v>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1815,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476874</v>
+        <v>476701</v>
       </c>
       <c r="R12" t="n">
-        <v>7044428</v>
+        <v>7044398</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,38 +1876,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026771</t>
+          <t>https://artportalen.se/Sighting/113026787</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113026772</v>
+        <v>113026789</v>
       </c>
       <c r="B13" t="n">
-        <v>97983</v>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1838,10 +1917,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476774</v>
+        <v>476725</v>
       </c>
       <c r="R13" t="n">
-        <v>7044383</v>
+        <v>7044414</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,7 +1978,5576 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/113026789</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113026790</v>
+      </c>
+      <c r="B14" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långan-Tornäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>476704</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7044407</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026790</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>113026791</v>
+      </c>
+      <c r="B15" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långan-Tornäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>476694</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7044369</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026791</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135890793</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92392</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>476954</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7044489</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135890793</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135889516</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96486</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2812</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kransmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hylocomiadelphus triquetrus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>476865</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7044458</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889516</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135887935</v>
+      </c>
+      <c r="B18" t="n">
+        <v>89290</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>476793</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7044602</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135887935</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135887747</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>476839</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7044561</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135887747</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135890276</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92011</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>476917</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7044438</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135890276</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>113026782</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Långan-Tornäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>476664</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7044374</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026782</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>113026784</v>
+      </c>
+      <c r="B22" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Långan-Tornäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>476748</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7044445</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026784</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135887305</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>476885</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7044557</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135887305</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135888884</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>476754</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7044651</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888884</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135889085</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>476694</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7044597</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889085</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135889333</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79441</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>476783</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7044546</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889333</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135888499</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>476772</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7044578</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888499</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135888120</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80556</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>476815</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7044589</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888120</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>113026760</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Långan-Tornäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>476908</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7044403</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026760</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135888337</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>476772</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7044582</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888337</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135888567</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>476766</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7044606</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888567</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135889256</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>476783</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7044546</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:53</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889256</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>135890496</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80561</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>476934</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7044411</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135890496</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>135888326</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80567</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>476767</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7044584</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888326</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135888134</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80568</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>476814</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7044588</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888134</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135888984</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>476754</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7044651</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Grovt bearbetad granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888984</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135888059</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>476798</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7044601</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Barkfläkt låga</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888059</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135888595</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>476761</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7044604</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Barkfläkta granar</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888595</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>135888744</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>476766</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7044622</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Skalad klen gran.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888744</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>135888896</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>476754</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7044651</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Barkfläkt och ringhackad gran</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888896</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>135889188</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>476747</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7044563</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Barkfläkta granar</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889188</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>135889243</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>476778</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7044558</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Flera barkskalade granar.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889243</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>135889343</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>476814</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7044521</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Barkfläkt gran</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889343</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>135890314</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>476916</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7044438</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Flera barkfläkta och skalade granar.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135890314</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>135888587</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>476762</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7044603</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Par i permanent revir?</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888587</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>135889674</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>476881</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7044438</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889674</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>135888848</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>476754</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7044651</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888848</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135888822</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>476754</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7044651</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888822</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>135888619</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99178</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>476761</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7044604</v>
+      </c>
+      <c r="S49" t="n">
+        <v>20</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888619</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>135889613</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99178</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>476865</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7044458</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889613</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>135889209</v>
+      </c>
+      <c r="B51" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>476778</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7044558</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Många i blom</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889209</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>135889164</v>
+      </c>
+      <c r="B52" t="n">
+        <v>106396</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>476747</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7044563</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889164</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>113026767</v>
+      </c>
+      <c r="B53" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Långan-Tornäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>476711</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7044397</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026767</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>113026771</v>
+      </c>
+      <c r="B54" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Långan-Tornäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>476874</v>
+      </c>
+      <c r="R54" t="n">
+        <v>7044428</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026771</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>113026772</v>
+      </c>
+      <c r="B55" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Långan-Tornäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>476774</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7044383</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/113026772</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>135888627</v>
+      </c>
+      <c r="B56" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>476761</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7044604</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888627</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135889141</v>
+      </c>
+      <c r="B57" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>476694</v>
+      </c>
+      <c r="R57" t="n">
+        <v>7044597</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889141</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>135889396</v>
+      </c>
+      <c r="B58" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>476814</v>
+      </c>
+      <c r="R58" t="n">
+        <v>7044521</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889396</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>135890358</v>
+      </c>
+      <c r="B59" t="n">
+        <v>99296</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>476916</v>
+      </c>
+      <c r="R59" t="n">
+        <v>7044438</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135890358</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>135888967</v>
+      </c>
+      <c r="B60" t="n">
+        <v>99551</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>476754</v>
+      </c>
+      <c r="R60" t="n">
+        <v>7044651</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888967</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>135889868</v>
+      </c>
+      <c r="B61" t="n">
+        <v>99080</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>476906</v>
+      </c>
+      <c r="R61" t="n">
+        <v>7044422</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889868</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>135889874</v>
+      </c>
+      <c r="B62" t="n">
+        <v>98325</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>476902</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7044424</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889874</t>
         </is>
       </c>
     </row>
@@ -1917,6 +7565,55 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31237-2026 artfynd.xlsx
+++ b/artfynd/A 31237-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ62"/>
+  <dimension ref="A1:AZ95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135890448</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,45 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135890254</v>
+        <v>135917624</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>87501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476919</v>
+        <v>476764</v>
       </c>
       <c r="R3" t="n">
-        <v>7044428</v>
+        <v>7044371</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ca 62cm bhd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,27 +892,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890254</t>
+          <t>https://artportalen.se/Sighting/135917624</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135888100</v>
+        <v>135890254</v>
       </c>
       <c r="B4" t="n">
-        <v>92044</v>
+        <v>92321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476816</v>
+        <v>476919</v>
       </c>
       <c r="R4" t="n">
-        <v>7044593</v>
+        <v>7044428</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,51 +1015,51 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888100</t>
+          <t>https://artportalen.se/Sighting/135890254</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113026757</v>
+        <v>135917629</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>92622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476964</v>
+        <v>476857</v>
       </c>
       <c r="R5" t="n">
-        <v>7044485</v>
+        <v>7044210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,12 +1086,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,27 +1116,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026757</t>
+          <t>https://artportalen.se/Sighting/135917629</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135888945</v>
+        <v>135888100</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>92046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1129,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1153,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476754</v>
+        <v>476816</v>
       </c>
       <c r="R6" t="n">
-        <v>7044651</v>
+        <v>7044593</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1188,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1198,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,16 +1239,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888945</t>
+          <t>https://artportalen.se/Sighting/135888100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135889310</v>
+        <v>135917622</v>
       </c>
       <c r="B7" t="n">
-        <v>92048</v>
+        <v>92046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,34 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476783</v>
+        <v>476813</v>
       </c>
       <c r="R7" t="n">
-        <v>7044546</v>
+        <v>7044315</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,27 +1340,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889310</t>
+          <t>https://artportalen.se/Sighting/135917622</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135890261</v>
+        <v>113026757</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,14 +1388,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Långan-Tornäs, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476916</v>
+        <v>476964</v>
       </c>
       <c r="R8" t="n">
-        <v>7044435</v>
+        <v>7044485</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,22 +1422,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,27 +1442,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890261</t>
+          <t>https://artportalen.se/Sighting/113026757</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135890410</v>
+        <v>135888945</v>
       </c>
       <c r="B9" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476916</v>
+        <v>476754</v>
       </c>
       <c r="R9" t="n">
-        <v>7044438</v>
+        <v>7044651</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,7 +1529,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1534,7 +1539,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1560,16 +1565,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890410</t>
+          <t>https://artportalen.se/Sighting/135888945</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135890469</v>
+        <v>135889310</v>
       </c>
       <c r="B10" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476934</v>
+        <v>476783</v>
       </c>
       <c r="R10" t="n">
-        <v>7044411</v>
+        <v>7044546</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1636,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1646,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,16 +1677,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890469</t>
+          <t>https://artportalen.se/Sighting/135889310</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113026786</v>
+        <v>135890261</v>
       </c>
       <c r="B11" t="n">
-        <v>83173</v>
+        <v>92050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1689,34 +1694,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476664</v>
+        <v>476916</v>
       </c>
       <c r="R11" t="n">
-        <v>7044378</v>
+        <v>7044435</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,12 +1748,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,27 +1778,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026786</t>
+          <t>https://artportalen.se/Sighting/135890261</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113026787</v>
+        <v>135890410</v>
       </c>
       <c r="B12" t="n">
-        <v>83173</v>
+        <v>92050</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,34 +1806,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476701</v>
+        <v>476916</v>
       </c>
       <c r="R12" t="n">
-        <v>7044398</v>
+        <v>7044438</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1845,12 +1860,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1865,27 +1890,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026787</t>
+          <t>https://artportalen.se/Sighting/135890410</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113026789</v>
+        <v>135890469</v>
       </c>
       <c r="B13" t="n">
-        <v>83173</v>
+        <v>92050</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1893,34 +1918,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476725</v>
+        <v>476934</v>
       </c>
       <c r="R13" t="n">
-        <v>7044414</v>
+        <v>7044411</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1947,12 +1972,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1967,27 +2002,27 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026789</t>
+          <t>https://artportalen.se/Sighting/135890469</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113026790</v>
+        <v>135917603</v>
       </c>
       <c r="B14" t="n">
-        <v>83173</v>
+        <v>92050</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1995,34 +2030,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476704</v>
+        <v>476827</v>
       </c>
       <c r="R14" t="n">
-        <v>7044407</v>
+        <v>7044565</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2049,12 +2084,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2069,27 +2114,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026790</t>
+          <t>https://artportalen.se/Sighting/135917603</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>113026791</v>
+        <v>135917607</v>
       </c>
       <c r="B15" t="n">
-        <v>83173</v>
+        <v>92050</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2097,34 +2142,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476694</v>
+        <v>476811</v>
       </c>
       <c r="R15" t="n">
-        <v>7044369</v>
+        <v>7044661</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,12 +2196,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2165,69 +2220,68 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026791</t>
+          <t>https://artportalen.se/Sighting/135917607</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135890793</v>
+        <v>113026786</v>
       </c>
       <c r="B16" t="n">
-        <v>92392</v>
+        <v>83173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2062</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Långan-Tornäs, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476954</v>
+        <v>476664</v>
       </c>
       <c r="R16" t="n">
-        <v>7044489</v>
+        <v>7044378</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2254,22 +2308,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2284,62 +2328,62 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890793</t>
+          <t>https://artportalen.se/Sighting/113026786</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135889516</v>
+        <v>113026787</v>
       </c>
       <c r="B17" t="n">
-        <v>96486</v>
+        <v>83173</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2812</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Långan-Tornäs, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476865</v>
+        <v>476701</v>
       </c>
       <c r="R17" t="n">
-        <v>7044458</v>
+        <v>7044398</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2366,22 +2410,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:05</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2396,27 +2430,27 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889516</t>
+          <t>https://artportalen.se/Sighting/113026787</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135887935</v>
+        <v>113026789</v>
       </c>
       <c r="B18" t="n">
-        <v>89290</v>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2424,37 +2458,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4412</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Långan-Tornäs, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476793</v>
+        <v>476725</v>
       </c>
       <c r="R18" t="n">
-        <v>7044602</v>
+        <v>7044414</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2478,22 +2512,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:54</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2508,65 +2532,65 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135887935</t>
+          <t>https://artportalen.se/Sighting/113026789</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135887747</v>
+        <v>113026790</v>
       </c>
       <c r="B19" t="n">
-        <v>92011</v>
+        <v>83173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Långan-Tornäs, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476839</v>
+        <v>476704</v>
       </c>
       <c r="R19" t="n">
-        <v>7044561</v>
+        <v>7044407</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2590,22 +2614,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>14:47</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2620,62 +2634,62 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135887747</t>
+          <t>https://artportalen.se/Sighting/113026790</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135890276</v>
+        <v>113026791</v>
       </c>
       <c r="B20" t="n">
-        <v>92011</v>
+        <v>83173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Långan-Tornäs, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476917</v>
+        <v>476694</v>
       </c>
       <c r="R20" t="n">
-        <v>7044438</v>
+        <v>7044369</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2702,22 +2716,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:38</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2726,33 +2730,34 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890276</t>
+          <t>https://artportalen.se/Sighting/113026791</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113026782</v>
+        <v>135890793</v>
       </c>
       <c r="B21" t="n">
-        <v>79327</v>
+        <v>92394</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2760,34 +2765,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476664</v>
+        <v>476954</v>
       </c>
       <c r="R21" t="n">
-        <v>7044374</v>
+        <v>7044489</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,12 +2819,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2834,62 +2849,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026782</t>
+          <t>https://artportalen.se/Sighting/135890793</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113026784</v>
+        <v>135917639</v>
       </c>
       <c r="B22" t="n">
-        <v>79327</v>
+        <v>80557</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476748</v>
+        <v>476977</v>
       </c>
       <c r="R22" t="n">
-        <v>7044445</v>
+        <v>7044492</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2916,12 +2931,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2936,49 +2961,49 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026784</t>
+          <t>https://artportalen.se/Sighting/135917639</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135887305</v>
+        <v>135889516</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>96488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2988,10 +3013,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476885</v>
+        <v>476865</v>
       </c>
       <c r="R23" t="n">
-        <v>7044557</v>
+        <v>7044458</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3023,7 +3048,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3033,7 +3058,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3059,51 +3084,51 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135887305</t>
+          <t>https://artportalen.se/Sighting/135889516</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135888884</v>
+        <v>135917605</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>92275</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476754</v>
+        <v>476822</v>
       </c>
       <c r="R24" t="n">
-        <v>7044651</v>
+        <v>7044613</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3135,7 +3160,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3145,7 +3170,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3160,49 +3185,49 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888884</t>
+          <t>https://artportalen.se/Sighting/135917605</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135889085</v>
+        <v>135887935</v>
       </c>
       <c r="B25" t="n">
-        <v>79441</v>
+        <v>89292</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3212,13 +3237,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476694</v>
+        <v>476793</v>
       </c>
       <c r="R25" t="n">
-        <v>7044597</v>
+        <v>7044602</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3247,7 +3272,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3257,7 +3282,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3283,51 +3308,51 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889085</t>
+          <t>https://artportalen.se/Sighting/135887935</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135889333</v>
+        <v>135917600</v>
       </c>
       <c r="B26" t="n">
-        <v>79441</v>
+        <v>89292</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476783</v>
+        <v>476832</v>
       </c>
       <c r="R26" t="n">
-        <v>7044546</v>
+        <v>7044558</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3359,7 +3384,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3369,7 +3394,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3384,27 +3409,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889333</t>
+          <t>https://artportalen.se/Sighting/135917600</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135888499</v>
+        <v>135917609</v>
       </c>
       <c r="B27" t="n">
-        <v>80060</v>
+        <v>89292</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3412,34 +3437,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>4412</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476772</v>
+        <v>476685</v>
       </c>
       <c r="R27" t="n">
-        <v>7044578</v>
+        <v>7044778</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3471,7 +3496,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3481,12 +3506,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På brandstubbe.</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3501,27 +3521,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888499</t>
+          <t>https://artportalen.se/Sighting/135917609</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135888120</v>
+        <v>135917632</v>
       </c>
       <c r="B28" t="n">
-        <v>80556</v>
+        <v>89292</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3529,34 +3549,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>4412</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476815</v>
+        <v>476916</v>
       </c>
       <c r="R28" t="n">
-        <v>7044589</v>
+        <v>7044298</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3588,7 +3608,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3598,7 +3618,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3613,27 +3633,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888120</t>
+          <t>https://artportalen.se/Sighting/135917632</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>113026760</v>
+        <v>135887747</v>
       </c>
       <c r="B29" t="n">
-        <v>80461</v>
+        <v>92013</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3641,37 +3661,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476908</v>
+        <v>476839</v>
       </c>
       <c r="R29" t="n">
-        <v>7044403</v>
+        <v>7044561</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3695,12 +3715,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3715,27 +3745,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026760</t>
+          <t>https://artportalen.se/Sighting/135887747</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135888337</v>
+        <v>135890276</v>
       </c>
       <c r="B30" t="n">
-        <v>80561</v>
+        <v>92013</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3743,21 +3773,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3767,10 +3797,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476772</v>
+        <v>476917</v>
       </c>
       <c r="R30" t="n">
-        <v>7044582</v>
+        <v>7044438</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3802,7 +3832,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3812,7 +3842,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3838,51 +3868,51 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888337</t>
+          <t>https://artportalen.se/Sighting/135890276</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135888567</v>
+        <v>113026782</v>
       </c>
       <c r="B31" t="n">
-        <v>80561</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Långan-Tornäs, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476766</v>
+        <v>476664</v>
       </c>
       <c r="R31" t="n">
-        <v>7044606</v>
+        <v>7044374</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3909,22 +3939,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>15:12</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>15:12</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3939,62 +3959,62 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888567</t>
+          <t>https://artportalen.se/Sighting/113026782</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135889256</v>
+        <v>113026784</v>
       </c>
       <c r="B32" t="n">
-        <v>80561</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Långan-Tornäs, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476783</v>
+        <v>476748</v>
       </c>
       <c r="R32" t="n">
-        <v>7044546</v>
+        <v>7044445</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4021,22 +4041,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4051,49 +4061,49 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889256</t>
+          <t>https://artportalen.se/Sighting/113026784</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135890496</v>
+        <v>135887305</v>
       </c>
       <c r="B33" t="n">
-        <v>80561</v>
+        <v>79441</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4103,10 +4113,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476934</v>
+        <v>476885</v>
       </c>
       <c r="R33" t="n">
-        <v>7044411</v>
+        <v>7044557</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4138,7 +4148,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4148,7 +4158,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4174,33 +4184,33 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890496</t>
+          <t>https://artportalen.se/Sighting/135887305</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135888326</v>
+        <v>135888884</v>
       </c>
       <c r="B34" t="n">
-        <v>80567</v>
+        <v>79441</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4215,10 +4225,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476767</v>
+        <v>476754</v>
       </c>
       <c r="R34" t="n">
-        <v>7044584</v>
+        <v>7044651</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4250,7 +4260,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4260,7 +4270,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4286,38 +4296,38 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888326</t>
+          <t>https://artportalen.se/Sighting/135888884</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135888134</v>
+        <v>135889085</v>
       </c>
       <c r="B35" t="n">
-        <v>80568</v>
+        <v>79441</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4327,10 +4337,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476814</v>
+        <v>476694</v>
       </c>
       <c r="R35" t="n">
-        <v>7044588</v>
+        <v>7044597</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4362,7 +4372,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4372,7 +4382,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4398,56 +4408,51 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888134</t>
+          <t>https://artportalen.se/Sighting/135889085</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135888984</v>
+        <v>135889333</v>
       </c>
       <c r="B36" t="n">
-        <v>57977</v>
+        <v>79441</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476754</v>
+        <v>476783</v>
       </c>
       <c r="R36" t="n">
-        <v>7044651</v>
+        <v>7044546</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4479,7 +4484,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4489,12 +4494,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Grovt bearbetad granhögstubbe</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4520,56 +4520,51 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888984</t>
+          <t>https://artportalen.se/Sighting/135889333</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135888059</v>
+        <v>135917634</v>
       </c>
       <c r="B37" t="n">
-        <v>57980</v>
+        <v>79441</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476798</v>
+        <v>477006</v>
       </c>
       <c r="R37" t="n">
-        <v>7044601</v>
+        <v>7044290</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4601,7 +4596,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4611,12 +4606,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Barkfläkt låga</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4631,67 +4621,62 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888059</t>
+          <t>https://artportalen.se/Sighting/135917634</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135888595</v>
+        <v>135917649</v>
       </c>
       <c r="B38" t="n">
-        <v>57980</v>
+        <v>79441</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476761</v>
+        <v>476998</v>
       </c>
       <c r="R38" t="n">
-        <v>7044604</v>
+        <v>7044769</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4723,7 +4708,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4733,12 +4718,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Barkfläkta granar</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4753,67 +4733,62 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888595</t>
+          <t>https://artportalen.se/Sighting/135917649</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135888744</v>
+        <v>135917650</v>
       </c>
       <c r="B39" t="n">
-        <v>57980</v>
+        <v>79441</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>476766</v>
+        <v>476984</v>
       </c>
       <c r="R39" t="n">
-        <v>7044622</v>
+        <v>7044785</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4845,7 +4820,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4855,12 +4830,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Skalad klen gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4875,67 +4850,62 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888744</t>
+          <t>https://artportalen.se/Sighting/135917650</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135888896</v>
+        <v>135917651</v>
       </c>
       <c r="B40" t="n">
-        <v>57980</v>
+        <v>79441</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>476754</v>
+        <v>476955</v>
       </c>
       <c r="R40" t="n">
-        <v>7044651</v>
+        <v>7044809</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4967,7 +4937,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4977,12 +4947,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Barkfläkt och ringhackad gran</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4997,67 +4967,62 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888896</t>
+          <t>https://artportalen.se/Sighting/135917651</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135889188</v>
+        <v>135917653</v>
       </c>
       <c r="B41" t="n">
-        <v>57980</v>
+        <v>79441</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>476747</v>
+        <v>476754</v>
       </c>
       <c r="R41" t="n">
-        <v>7044563</v>
+        <v>7044898</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5089,7 +5054,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5099,12 +5064,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Barkfläkta granar</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5119,67 +5084,62 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889188</t>
+          <t>https://artportalen.se/Sighting/135917653</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135889243</v>
+        <v>135917655</v>
       </c>
       <c r="B42" t="n">
-        <v>57980</v>
+        <v>79441</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>476778</v>
+        <v>476732</v>
       </c>
       <c r="R42" t="n">
-        <v>7044558</v>
+        <v>7044931</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5211,7 +5171,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5221,12 +5181,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Flera barkskalade granar.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5241,67 +5201,62 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889243</t>
+          <t>https://artportalen.se/Sighting/135917655</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135889343</v>
+        <v>135917663</v>
       </c>
       <c r="B43" t="n">
-        <v>57980</v>
+        <v>79441</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>476814</v>
+        <v>476740</v>
       </c>
       <c r="R43" t="n">
-        <v>7044521</v>
+        <v>7044997</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5333,7 +5288,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5343,12 +5298,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Barkfläkt gran</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5363,67 +5318,62 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889343</t>
+          <t>https://artportalen.se/Sighting/135917663</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135890314</v>
+        <v>135917664</v>
       </c>
       <c r="B44" t="n">
-        <v>57980</v>
+        <v>79441</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>476916</v>
+        <v>476718</v>
       </c>
       <c r="R44" t="n">
-        <v>7044438</v>
+        <v>7044987</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5455,7 +5405,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5465,12 +5415,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Flera barkfläkta och skalade granar.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5485,71 +5435,62 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890314</t>
+          <t>https://artportalen.se/Sighting/135917664</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135888587</v>
+        <v>135917666</v>
       </c>
       <c r="B45" t="n">
-        <v>58141</v>
+        <v>79441</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>476762</v>
+        <v>476713</v>
       </c>
       <c r="R45" t="n">
-        <v>7044603</v>
+        <v>7044947</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5581,7 +5522,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5591,12 +5532,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Par i permanent revir?</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5611,27 +5552,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888587</t>
+          <t>https://artportalen.se/Sighting/135917666</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135889674</v>
+        <v>135888499</v>
       </c>
       <c r="B46" t="n">
-        <v>58141</v>
+        <v>80060</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5639,43 +5580,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>476881</v>
+        <v>476772</v>
       </c>
       <c r="R46" t="n">
-        <v>7044438</v>
+        <v>7044578</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5707,7 +5639,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5717,7 +5649,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5743,38 +5680,38 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889674</t>
+          <t>https://artportalen.se/Sighting/135888499</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135888848</v>
+        <v>135888120</v>
       </c>
       <c r="B47" t="n">
-        <v>99276</v>
+        <v>80556</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219811</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5784,10 +5721,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>476754</v>
+        <v>476815</v>
       </c>
       <c r="R47" t="n">
-        <v>7044651</v>
+        <v>7044589</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5819,7 +5756,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5829,7 +5766,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5855,51 +5792,51 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888848</t>
+          <t>https://artportalen.se/Sighting/135888120</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135888822</v>
+        <v>135917620</v>
       </c>
       <c r="B48" t="n">
-        <v>99298</v>
+        <v>80556</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219847</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>476754</v>
+        <v>476796</v>
       </c>
       <c r="R48" t="n">
-        <v>7044651</v>
+        <v>7044305</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5931,7 +5868,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5941,7 +5878,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5956,70 +5893,65 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888822</t>
+          <t>https://artportalen.se/Sighting/135917620</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135888619</v>
+        <v>135917631</v>
       </c>
       <c r="B49" t="n">
-        <v>99178</v>
+        <v>80556</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220093</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476761</v>
+        <v>476919</v>
       </c>
       <c r="R49" t="n">
-        <v>7044604</v>
+        <v>7044298</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6048,7 +5980,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6058,7 +5990,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6073,27 +6005,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888619</t>
+          <t>https://artportalen.se/Sighting/135917631</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135889613</v>
+        <v>113026760</v>
       </c>
       <c r="B50" t="n">
-        <v>99178</v>
+        <v>80461</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6101,34 +6033,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220093</v>
+        <v>6462</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Långan-Tornäs, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>476865</v>
+        <v>476908</v>
       </c>
       <c r="R50" t="n">
-        <v>7044458</v>
+        <v>7044403</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6155,22 +6087,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:06</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:06</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6185,71 +6107,62 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889613</t>
+          <t>https://artportalen.se/Sighting/113026760</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135889209</v>
+        <v>135888337</v>
       </c>
       <c r="B51" t="n">
-        <v>99274</v>
+        <v>80561</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>476778</v>
+        <v>476772</v>
       </c>
       <c r="R51" t="n">
-        <v>7044558</v>
+        <v>7044582</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6281,7 +6194,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6291,12 +6204,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Många i blom</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6322,16 +6230,16 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889209</t>
+          <t>https://artportalen.se/Sighting/135888337</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135889164</v>
+        <v>135888567</v>
       </c>
       <c r="B52" t="n">
-        <v>106396</v>
+        <v>80561</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6339,48 +6247,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221725</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>476747</v>
+        <v>476766</v>
       </c>
       <c r="R52" t="n">
-        <v>7044563</v>
+        <v>7044606</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6412,7 +6306,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6422,7 +6316,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6448,16 +6342,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889164</t>
+          <t>https://artportalen.se/Sighting/135888567</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>113026767</v>
+        <v>135889256</v>
       </c>
       <c r="B53" t="n">
-        <v>97983</v>
+        <v>80561</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6465,34 +6359,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>476711</v>
+        <v>476783</v>
       </c>
       <c r="R53" t="n">
-        <v>7044397</v>
+        <v>7044546</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6519,12 +6413,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6539,27 +6443,27 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026767</t>
+          <t>https://artportalen.se/Sighting/135889256</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>113026771</v>
+        <v>135890496</v>
       </c>
       <c r="B54" t="n">
-        <v>97983</v>
+        <v>80561</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6567,34 +6471,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>476874</v>
+        <v>476934</v>
       </c>
       <c r="R54" t="n">
-        <v>7044428</v>
+        <v>7044411</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6621,12 +6525,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6641,27 +6555,27 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026771</t>
+          <t>https://artportalen.se/Sighting/135890496</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113026772</v>
+        <v>135917621</v>
       </c>
       <c r="B55" t="n">
-        <v>97983</v>
+        <v>80561</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6669,34 +6583,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221945</v>
+        <v>6462</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>476774</v>
+        <v>476796</v>
       </c>
       <c r="R55" t="n">
-        <v>7044383</v>
+        <v>7044304</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6723,12 +6637,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6743,27 +6667,27 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026772</t>
+          <t>https://artportalen.se/Sighting/135917621</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135888627</v>
+        <v>135888326</v>
       </c>
       <c r="B56" t="n">
-        <v>99296</v>
+        <v>80567</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6771,21 +6695,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6795,10 +6719,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>476761</v>
+        <v>476767</v>
       </c>
       <c r="R56" t="n">
-        <v>7044604</v>
+        <v>7044584</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6830,7 +6754,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6840,7 +6764,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6866,16 +6790,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888627</t>
+          <t>https://artportalen.se/Sighting/135888326</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135889141</v>
+        <v>135888134</v>
       </c>
       <c r="B57" t="n">
-        <v>99296</v>
+        <v>80568</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6883,21 +6807,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6907,10 +6831,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>476694</v>
+        <v>476814</v>
       </c>
       <c r="R57" t="n">
-        <v>7044597</v>
+        <v>7044588</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6942,7 +6866,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6952,7 +6876,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6978,16 +6902,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889141</t>
+          <t>https://artportalen.se/Sighting/135888134</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135889396</v>
+        <v>135888984</v>
       </c>
       <c r="B58" t="n">
-        <v>99296</v>
+        <v>57977</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6995,34 +6919,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221952</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>476814</v>
+        <v>476754</v>
       </c>
       <c r="R58" t="n">
-        <v>7044521</v>
+        <v>7044651</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7054,7 +6983,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7064,7 +6993,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Grovt bearbetad granhögstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7090,48 +7024,44 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889396</t>
+          <t>https://artportalen.se/Sighting/135888984</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135890358</v>
+        <v>135888059</v>
       </c>
       <c r="B59" t="n">
-        <v>99296</v>
+        <v>57980</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221952</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7140,10 +7070,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>476916</v>
+        <v>476798</v>
       </c>
       <c r="R59" t="n">
-        <v>7044438</v>
+        <v>7044601</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7175,7 +7105,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7185,7 +7115,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Barkfläkt låga</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7211,51 +7146,56 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890358</t>
+          <t>https://artportalen.se/Sighting/135888059</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135888967</v>
+        <v>135888595</v>
       </c>
       <c r="B60" t="n">
-        <v>99551</v>
+        <v>57980</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222812</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>476754</v>
+        <v>476761</v>
       </c>
       <c r="R60" t="n">
-        <v>7044651</v>
+        <v>7044604</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7287,7 +7227,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7297,7 +7237,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Barkfläkta granar</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7323,51 +7268,56 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888967</t>
+          <t>https://artportalen.se/Sighting/135888595</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135889868</v>
+        <v>135888744</v>
       </c>
       <c r="B61" t="n">
-        <v>99080</v>
+        <v>57980</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>223049</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>476906</v>
+        <v>476766</v>
       </c>
       <c r="R61" t="n">
-        <v>7044422</v>
+        <v>7044622</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7399,7 +7349,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7409,7 +7359,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Skalad klen gran.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7435,51 +7390,56 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889868</t>
+          <t>https://artportalen.se/Sighting/135888744</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135889874</v>
+        <v>135888896</v>
       </c>
       <c r="B62" t="n">
-        <v>98325</v>
+        <v>57980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>223358</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>476902</v>
+        <v>476754</v>
       </c>
       <c r="R62" t="n">
-        <v>7044424</v>
+        <v>7044651</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7511,7 +7471,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7521,7 +7481,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Barkfläkt och ringhackad gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7546,6 +7511,3887 @@
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888896</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>135889188</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>476747</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7044563</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Barkfläkta granar</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889188</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>135889243</v>
+      </c>
+      <c r="B64" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>476778</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7044558</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Flera barkskalade granar.</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889243</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>135889343</v>
+      </c>
+      <c r="B65" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>476814</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7044521</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Barkfläkt gran</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889343</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>135890314</v>
+      </c>
+      <c r="B66" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>476916</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7044438</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Flera barkfläkta och skalade granar.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135890314</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>135917612</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lundsjön N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>476712</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7044375</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917612</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>135917618</v>
+      </c>
+      <c r="B68" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lundsjön N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>476783</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7044308</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917618</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>135917637</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lundsjön N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>476966</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7044462</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917637</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>135917656</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lundsjön N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>476723</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7044923</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>18:58</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917656</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135917657</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lundsjön N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>476729</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7044916</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917657</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135917659</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lundsjön N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>476738</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7044973</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917659</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135917661</v>
+      </c>
+      <c r="B73" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lundsjön N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>476737</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7044989</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917661</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135917668</v>
+      </c>
+      <c r="B74" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lundsjön N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>476706</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7044899</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917668</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135917669</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lundsjön N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>476694</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7044903</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917669</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135917641</v>
+      </c>
+      <c r="B76" t="n">
+        <v>57158</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lundsjön N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>476955</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7044640</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917641</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135888587</v>
+      </c>
+      <c r="B77" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>476762</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7044603</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Par i permanent revir?</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888587</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135889674</v>
+      </c>
+      <c r="B78" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>476881</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7044438</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889674</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135888848</v>
+      </c>
+      <c r="B79" t="n">
+        <v>99278</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>476754</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7044651</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888848</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135888822</v>
+      </c>
+      <c r="B80" t="n">
+        <v>99300</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>476754</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7044651</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888822</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135888619</v>
+      </c>
+      <c r="B81" t="n">
+        <v>99180</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>476761</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7044604</v>
+      </c>
+      <c r="S81" t="n">
+        <v>20</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888619</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135889613</v>
+      </c>
+      <c r="B82" t="n">
+        <v>99180</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>220093</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Korallrot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Corallorhiza trifida</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>476865</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7044458</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889613</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135889209</v>
+      </c>
+      <c r="B83" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>476778</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7044558</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Många i blom</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889209</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135889164</v>
+      </c>
+      <c r="B84" t="n">
+        <v>106398</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>476747</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7044563</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889164</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>113026767</v>
+      </c>
+      <c r="B85" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Långan-Tornäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>476711</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7044397</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026767</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>113026771</v>
+      </c>
+      <c r="B86" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Långan-Tornäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>476874</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7044428</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026771</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>113026772</v>
+      </c>
+      <c r="B87" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Långan-Tornäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>476774</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7044383</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2023-10-16</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>August Alvtegen</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113026772</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>135888627</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>476761</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7044604</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888627</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>135889141</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>476694</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7044597</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889141</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>135889396</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>476814</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7044521</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889396</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>135890358</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>476916</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7044438</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>16:42</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135890358</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>135917602</v>
+      </c>
+      <c r="B92" t="n">
+        <v>99298</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Lundsjön N, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>476830</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7044560</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135917602</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>135888967</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99553</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>222812</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Liljekonvalj</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Convallaria majalis</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>476754</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7044651</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135888967</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>135889868</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99082</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>476906</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7044422</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135889868</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>135889874</v>
+      </c>
+      <c r="B95" t="n">
+        <v>98327</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Storrönningen, Storrönningen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>476902</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7044424</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135889874</t>
         </is>
@@ -7614,6 +11460,39 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31237-2026 artfynd.xlsx
+++ b/artfynd/A 31237-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ154"/>
+  <dimension ref="A1:AZ153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,45 +792,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135917624</v>
+        <v>135944192</v>
       </c>
       <c r="B3" t="n">
-        <v>87501</v>
+        <v>89428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>449</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476764</v>
+        <v>477006</v>
       </c>
       <c r="R3" t="n">
-        <v>7044371</v>
+        <v>7044292</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,24 +860,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>16:31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ca 62cm bhd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,27 +877,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917624</t>
+          <t>https://artportalen.se/Sighting/135944192</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135944192</v>
+        <v>135890254</v>
       </c>
       <c r="B4" t="n">
-        <v>89428</v>
+        <v>92321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,34 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lundsjön, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477006</v>
+        <v>476919</v>
       </c>
       <c r="R4" t="n">
-        <v>7044292</v>
+        <v>7044428</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,9 +962,19 @@
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,62 +989,62 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944192</t>
+          <t>https://artportalen.se/Sighting/135890254</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135890254</v>
+        <v>135917629</v>
       </c>
       <c r="B5" t="n">
-        <v>92321</v>
+        <v>92622</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>760</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476919</v>
+        <v>476857</v>
       </c>
       <c r="R5" t="n">
-        <v>7044428</v>
+        <v>7044210</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,62 +1101,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890254</t>
+          <t>https://artportalen.se/Sighting/135917629</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135917629</v>
+        <v>135888100</v>
       </c>
       <c r="B6" t="n">
-        <v>92622</v>
+        <v>92046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>760</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476857</v>
+        <v>476816</v>
       </c>
       <c r="R6" t="n">
-        <v>7044210</v>
+        <v>7044593</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1188,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1198,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,24 +1213,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917629</t>
+          <t>https://artportalen.se/Sighting/135888100</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135888100</v>
+        <v>135917622</v>
       </c>
       <c r="B7" t="n">
         <v>92046</v>
@@ -1266,14 +1261,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476816</v>
+        <v>476813</v>
       </c>
       <c r="R7" t="n">
-        <v>7044593</v>
+        <v>7044315</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,27 +1325,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888100</t>
+          <t>https://artportalen.se/Sighting/135917622</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135917622</v>
+        <v>113026757</v>
       </c>
       <c r="B8" t="n">
-        <v>92046</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,34 +1353,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Långan-Tornäs, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476813</v>
+        <v>476964</v>
       </c>
       <c r="R8" t="n">
-        <v>7044315</v>
+        <v>7044485</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,22 +1407,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:27</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,27 +1427,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917622</t>
+          <t>https://artportalen.se/Sighting/113026757</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113026757</v>
+        <v>135888945</v>
       </c>
       <c r="B9" t="n">
-        <v>91909</v>
+        <v>92050</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,14 +1475,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476964</v>
+        <v>476754</v>
       </c>
       <c r="R9" t="n">
-        <v>7044485</v>
+        <v>7044651</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1524,12 +1509,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,24 +1539,24 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026757</t>
+          <t>https://artportalen.se/Sighting/135888945</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135888945</v>
+        <v>135889310</v>
       </c>
       <c r="B10" t="n">
         <v>92050</v>
@@ -1596,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476754</v>
+        <v>476783</v>
       </c>
       <c r="R10" t="n">
-        <v>7044651</v>
+        <v>7044546</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1631,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1641,7 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,13 +1662,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888945</t>
+          <t>https://artportalen.se/Sighting/135889310</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135889310</v>
+        <v>135890261</v>
       </c>
       <c r="B11" t="n">
         <v>92050</v>
@@ -1708,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476783</v>
+        <v>476916</v>
       </c>
       <c r="R11" t="n">
-        <v>7044546</v>
+        <v>7044435</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,7 +1738,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1753,7 +1748,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1779,13 +1774,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889310</t>
+          <t>https://artportalen.se/Sighting/135890261</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135890261</v>
+        <v>135890410</v>
       </c>
       <c r="B12" t="n">
         <v>92050</v>
@@ -1823,7 +1818,7 @@
         <v>476916</v>
       </c>
       <c r="R12" t="n">
-        <v>7044435</v>
+        <v>7044438</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1850,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,7 +1860,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1891,13 +1886,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890261</t>
+          <t>https://artportalen.se/Sighting/135890410</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135890410</v>
+        <v>135890469</v>
       </c>
       <c r="B13" t="n">
         <v>92050</v>
@@ -1932,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476916</v>
+        <v>476934</v>
       </c>
       <c r="R13" t="n">
-        <v>7044438</v>
+        <v>7044411</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1967,7 +1962,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1977,7 +1972,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,13 +1998,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890410</t>
+          <t>https://artportalen.se/Sighting/135890469</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135890469</v>
+        <v>135917603</v>
       </c>
       <c r="B14" t="n">
         <v>92050</v>
@@ -2040,14 +2035,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476934</v>
+        <v>476827</v>
       </c>
       <c r="R14" t="n">
-        <v>7044411</v>
+        <v>7044565</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2079,7 +2074,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2089,7 +2084,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2104,24 +2099,24 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890469</t>
+          <t>https://artportalen.se/Sighting/135917603</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135917603</v>
+        <v>135917607</v>
       </c>
       <c r="B15" t="n">
         <v>92050</v>
@@ -2156,10 +2151,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476827</v>
+        <v>476811</v>
       </c>
       <c r="R15" t="n">
-        <v>7044565</v>
+        <v>7044661</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,7 +2186,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2201,7 +2196,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2227,13 +2222,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917603</t>
+          <t>https://artportalen.se/Sighting/135917607</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135917607</v>
+        <v>135945068</v>
       </c>
       <c r="B16" t="n">
         <v>92050</v>
@@ -2268,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476811</v>
+        <v>476936</v>
       </c>
       <c r="R16" t="n">
-        <v>7044661</v>
+        <v>7044672</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2301,19 +2296,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:17</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,38 +2324,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917607</t>
+          <t>https://artportalen.se/Sighting/135945068</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135945068</v>
+        <v>135945090</v>
       </c>
       <c r="B17" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2380,10 +2365,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476936</v>
+        <v>476930</v>
       </c>
       <c r="R17" t="n">
-        <v>7044672</v>
+        <v>7044430</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2441,51 +2426,51 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945068</t>
+          <t>https://artportalen.se/Sighting/135945090</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135945090</v>
+        <v>113026786</v>
       </c>
       <c r="B18" t="n">
-        <v>92064</v>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Långan-Tornäs, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476930</v>
+        <v>476664</v>
       </c>
       <c r="R18" t="n">
-        <v>7044430</v>
+        <v>7044378</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,12 +2497,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2532,24 +2517,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945090</t>
+          <t>https://artportalen.se/Sighting/113026786</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>113026786</v>
+        <v>113026787</v>
       </c>
       <c r="B19" t="n">
         <v>83173</v>
@@ -2584,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476664</v>
+        <v>476701</v>
       </c>
       <c r="R19" t="n">
-        <v>7044378</v>
+        <v>7044398</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2645,13 +2630,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026786</t>
+          <t>https://artportalen.se/Sighting/113026787</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113026787</v>
+        <v>113026789</v>
       </c>
       <c r="B20" t="n">
         <v>83173</v>
@@ -2686,10 +2671,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476701</v>
+        <v>476725</v>
       </c>
       <c r="R20" t="n">
-        <v>7044398</v>
+        <v>7044414</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2747,13 +2732,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026787</t>
+          <t>https://artportalen.se/Sighting/113026789</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>113026789</v>
+        <v>113026790</v>
       </c>
       <c r="B21" t="n">
         <v>83173</v>
@@ -2788,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476725</v>
+        <v>476704</v>
       </c>
       <c r="R21" t="n">
-        <v>7044414</v>
+        <v>7044407</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2849,13 +2834,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026789</t>
+          <t>https://artportalen.se/Sighting/113026790</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>113026790</v>
+        <v>113026791</v>
       </c>
       <c r="B22" t="n">
         <v>83173</v>
@@ -2890,10 +2875,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476704</v>
+        <v>476694</v>
       </c>
       <c r="R22" t="n">
-        <v>7044407</v>
+        <v>7044369</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2934,6 +2919,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2951,51 +2937,51 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026790</t>
+          <t>https://artportalen.se/Sighting/113026791</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>113026791</v>
+        <v>135890793</v>
       </c>
       <c r="B23" t="n">
-        <v>83173</v>
+        <v>92394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>2062</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476694</v>
+        <v>476954</v>
       </c>
       <c r="R23" t="n">
-        <v>7044369</v>
+        <v>7044489</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3022,12 +3008,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3036,69 +3032,68 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026791</t>
+          <t>https://artportalen.se/Sighting/135890793</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135890793</v>
+        <v>135917639</v>
       </c>
       <c r="B24" t="n">
-        <v>92394</v>
+        <v>80557</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2062</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476954</v>
+        <v>476977</v>
       </c>
       <c r="R24" t="n">
-        <v>7044489</v>
+        <v>7044492</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,7 +3125,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3140,7 +3135,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3155,24 +3150,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890793</t>
+          <t>https://artportalen.se/Sighting/135917639</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135917639</v>
+        <v>135944181</v>
       </c>
       <c r="B25" t="n">
         <v>80557</v>
@@ -3203,14 +3198,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476977</v>
+        <v>476997</v>
       </c>
       <c r="R25" t="n">
-        <v>7044492</v>
+        <v>7044273</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3240,19 +3235,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>17:52</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>17:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3267,24 +3252,24 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917639</t>
+          <t>https://artportalen.se/Sighting/135944181</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135944181</v>
+        <v>135945080</v>
       </c>
       <c r="B26" t="n">
         <v>80557</v>
@@ -3315,14 +3300,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lundsjön, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476997</v>
+        <v>476928</v>
       </c>
       <c r="R26" t="n">
-        <v>7044273</v>
+        <v>7044299</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3369,24 +3354,24 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944181</t>
+          <t>https://artportalen.se/Sighting/135945080</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135945080</v>
+        <v>135945081</v>
       </c>
       <c r="B27" t="n">
         <v>80557</v>
@@ -3421,10 +3406,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476928</v>
+        <v>476864</v>
       </c>
       <c r="R27" t="n">
-        <v>7044299</v>
+        <v>7044328</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3482,13 +3467,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945080</t>
+          <t>https://artportalen.se/Sighting/135945081</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135945081</v>
+        <v>135945082</v>
       </c>
       <c r="B28" t="n">
         <v>80557</v>
@@ -3523,10 +3508,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476864</v>
+        <v>476923</v>
       </c>
       <c r="R28" t="n">
-        <v>7044328</v>
+        <v>7044381</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,13 +3569,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945081</t>
+          <t>https://artportalen.se/Sighting/135945082</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135945082</v>
+        <v>135945083</v>
       </c>
       <c r="B29" t="n">
         <v>80557</v>
@@ -3625,10 +3610,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476923</v>
+        <v>476929</v>
       </c>
       <c r="R29" t="n">
-        <v>7044381</v>
+        <v>7044367</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3686,13 +3671,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945082</t>
+          <t>https://artportalen.se/Sighting/135945083</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135945083</v>
+        <v>135945084</v>
       </c>
       <c r="B30" t="n">
         <v>80557</v>
@@ -3727,10 +3712,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476929</v>
+        <v>476931</v>
       </c>
       <c r="R30" t="n">
-        <v>7044367</v>
+        <v>7044441</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3788,51 +3773,51 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945083</t>
+          <t>https://artportalen.se/Sighting/135945084</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135945084</v>
+        <v>135889516</v>
       </c>
       <c r="B31" t="n">
-        <v>80557</v>
+        <v>96488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>2812</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476931</v>
+        <v>476865</v>
       </c>
       <c r="R31" t="n">
-        <v>7044441</v>
+        <v>7044458</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3862,9 +3847,19 @@
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3879,24 +3874,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945084</t>
+          <t>https://artportalen.se/Sighting/135889516</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135889516</v>
+        <v>135944174</v>
       </c>
       <c r="B32" t="n">
         <v>96488</v>
@@ -3927,14 +3922,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476865</v>
+        <v>476992</v>
       </c>
       <c r="R32" t="n">
-        <v>7044458</v>
+        <v>7044208</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3964,19 +3959,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3991,27 +3976,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889516</t>
+          <t>https://artportalen.se/Sighting/135944174</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135944174</v>
+        <v>135917605</v>
       </c>
       <c r="B33" t="n">
-        <v>96488</v>
+        <v>92275</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4019,34 +4004,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2812</v>
+        <v>3298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lundsjön, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476992</v>
+        <v>476822</v>
       </c>
       <c r="R33" t="n">
-        <v>7044208</v>
+        <v>7044613</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4076,9 +4061,19 @@
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4093,24 +4088,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944174</t>
+          <t>https://artportalen.se/Sighting/135917605</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135917605</v>
+        <v>135944194</v>
       </c>
       <c r="B34" t="n">
         <v>92275</v>
@@ -4141,14 +4136,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476822</v>
+        <v>477012</v>
       </c>
       <c r="R34" t="n">
-        <v>7044613</v>
+        <v>7044311</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4178,19 +4173,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4205,65 +4190,65 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917605</t>
+          <t>https://artportalen.se/Sighting/135944194</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135944194</v>
+        <v>135887935</v>
       </c>
       <c r="B35" t="n">
-        <v>92275</v>
+        <v>89292</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3298</v>
+        <v>4412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lundsjön, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>477012</v>
+        <v>476793</v>
       </c>
       <c r="R35" t="n">
-        <v>7044311</v>
+        <v>7044602</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4290,9 +4275,19 @@
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4307,24 +4302,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944194</t>
+          <t>https://artportalen.se/Sighting/135887935</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135887935</v>
+        <v>135917600</v>
       </c>
       <c r="B36" t="n">
         <v>89292</v>
@@ -4355,17 +4350,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476793</v>
+        <v>476832</v>
       </c>
       <c r="R36" t="n">
-        <v>7044602</v>
+        <v>7044558</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4394,7 +4389,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4404,7 +4399,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4419,24 +4414,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135887935</t>
+          <t>https://artportalen.se/Sighting/135917600</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135917600</v>
+        <v>135917609</v>
       </c>
       <c r="B37" t="n">
         <v>89292</v>
@@ -4471,10 +4466,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476832</v>
+        <v>476685</v>
       </c>
       <c r="R37" t="n">
-        <v>7044558</v>
+        <v>7044778</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4506,7 +4501,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4516,7 +4511,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4542,13 +4537,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917600</t>
+          <t>https://artportalen.se/Sighting/135917609</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135917609</v>
+        <v>135917632</v>
       </c>
       <c r="B38" t="n">
         <v>89292</v>
@@ -4583,10 +4578,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476685</v>
+        <v>476916</v>
       </c>
       <c r="R38" t="n">
-        <v>7044778</v>
+        <v>7044298</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4618,7 +4613,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4628,7 +4623,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4654,13 +4649,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917609</t>
+          <t>https://artportalen.se/Sighting/135917632</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135917632</v>
+        <v>135944171</v>
       </c>
       <c r="B39" t="n">
         <v>89292</v>
@@ -4691,14 +4686,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>476916</v>
+        <v>476879</v>
       </c>
       <c r="R39" t="n">
-        <v>7044298</v>
+        <v>7044712</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4728,19 +4723,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>17:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4755,24 +4740,24 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917632</t>
+          <t>https://artportalen.se/Sighting/135944171</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135944171</v>
+        <v>135944197</v>
       </c>
       <c r="B40" t="n">
         <v>89292</v>
@@ -4807,10 +4792,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>476879</v>
+        <v>476990</v>
       </c>
       <c r="R40" t="n">
-        <v>7044712</v>
+        <v>7044274</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4868,13 +4853,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944171</t>
+          <t>https://artportalen.se/Sighting/135944197</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135944197</v>
+        <v>135945066</v>
       </c>
       <c r="B41" t="n">
         <v>89292</v>
@@ -4905,14 +4890,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lundsjön, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>476990</v>
+        <v>476919</v>
       </c>
       <c r="R41" t="n">
-        <v>7044274</v>
+        <v>7044298</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4959,24 +4944,24 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944197</t>
+          <t>https://artportalen.se/Sighting/135945066</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135945066</v>
+        <v>135945067</v>
       </c>
       <c r="B42" t="n">
         <v>89292</v>
@@ -5011,10 +4996,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>476919</v>
+        <v>476860</v>
       </c>
       <c r="R42" t="n">
-        <v>7044298</v>
+        <v>7044340</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5072,54 +5057,54 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945066</t>
+          <t>https://artportalen.se/Sighting/135945067</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135945067</v>
+        <v>135887747</v>
       </c>
       <c r="B43" t="n">
-        <v>89292</v>
+        <v>92013</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4412</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>476860</v>
+        <v>476839</v>
       </c>
       <c r="R43" t="n">
-        <v>7044340</v>
+        <v>7044561</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5146,9 +5131,19 @@
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5163,24 +5158,24 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945067</t>
+          <t>https://artportalen.se/Sighting/135887747</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135887747</v>
+        <v>135890276</v>
       </c>
       <c r="B44" t="n">
         <v>92013</v>
@@ -5215,13 +5210,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>476839</v>
+        <v>476917</v>
       </c>
       <c r="R44" t="n">
-        <v>7044561</v>
+        <v>7044438</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5250,7 +5245,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5260,7 +5255,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5286,13 +5281,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135887747</t>
+          <t>https://artportalen.se/Sighting/135890276</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135890276</v>
+        <v>135944200</v>
       </c>
       <c r="B45" t="n">
         <v>92013</v>
@@ -5323,14 +5318,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>476917</v>
+        <v>476860</v>
       </c>
       <c r="R45" t="n">
-        <v>7044438</v>
+        <v>7044112</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5360,19 +5355,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>16:38</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>16:38</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5387,62 +5372,62 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890276</t>
+          <t>https://artportalen.se/Sighting/135944200</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135944200</v>
+        <v>113026782</v>
       </c>
       <c r="B46" t="n">
-        <v>92013</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lundsjön, Jmt</t>
+          <t>Långan-Tornäs, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>476860</v>
+        <v>476664</v>
       </c>
       <c r="R46" t="n">
-        <v>7044112</v>
+        <v>7044374</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5469,12 +5454,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5489,24 +5474,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944200</t>
+          <t>https://artportalen.se/Sighting/113026782</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>113026782</v>
+        <v>113026784</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5541,10 +5526,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>476664</v>
+        <v>476748</v>
       </c>
       <c r="R47" t="n">
-        <v>7044374</v>
+        <v>7044445</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5602,16 +5587,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026782</t>
+          <t>https://artportalen.se/Sighting/113026784</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>113026784</v>
+        <v>135887305</v>
       </c>
       <c r="B48" t="n">
-        <v>79327</v>
+        <v>79441</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5639,14 +5624,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>476748</v>
+        <v>476885</v>
       </c>
       <c r="R48" t="n">
-        <v>7044445</v>
+        <v>7044557</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5673,12 +5658,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5693,24 +5688,24 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026784</t>
+          <t>https://artportalen.se/Sighting/135887305</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135887305</v>
+        <v>135888884</v>
       </c>
       <c r="B49" t="n">
         <v>79441</v>
@@ -5745,10 +5740,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>476885</v>
+        <v>476754</v>
       </c>
       <c r="R49" t="n">
-        <v>7044557</v>
+        <v>7044651</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5780,7 +5775,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5790,7 +5785,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5816,13 +5811,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135887305</t>
+          <t>https://artportalen.se/Sighting/135888884</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135888884</v>
+        <v>135889085</v>
       </c>
       <c r="B50" t="n">
         <v>79441</v>
@@ -5857,10 +5852,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>476754</v>
+        <v>476694</v>
       </c>
       <c r="R50" t="n">
-        <v>7044651</v>
+        <v>7044597</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5892,7 +5887,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5902,7 +5897,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5928,13 +5923,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888884</t>
+          <t>https://artportalen.se/Sighting/135889085</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135889085</v>
+        <v>135889333</v>
       </c>
       <c r="B51" t="n">
         <v>79441</v>
@@ -5969,10 +5964,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>476694</v>
+        <v>476783</v>
       </c>
       <c r="R51" t="n">
-        <v>7044597</v>
+        <v>7044546</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6004,7 +5999,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6014,7 +6009,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6040,13 +6035,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889085</t>
+          <t>https://artportalen.se/Sighting/135889333</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135889333</v>
+        <v>135917634</v>
       </c>
       <c r="B52" t="n">
         <v>79441</v>
@@ -6077,14 +6072,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>476783</v>
+        <v>477006</v>
       </c>
       <c r="R52" t="n">
-        <v>7044546</v>
+        <v>7044290</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6116,7 +6111,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6126,7 +6121,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6141,24 +6136,24 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889333</t>
+          <t>https://artportalen.se/Sighting/135917634</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135917634</v>
+        <v>135917649</v>
       </c>
       <c r="B53" t="n">
         <v>79441</v>
@@ -6193,10 +6188,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>477006</v>
+        <v>476998</v>
       </c>
       <c r="R53" t="n">
-        <v>7044290</v>
+        <v>7044769</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6228,7 +6223,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6238,7 +6233,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6264,13 +6259,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917634</t>
+          <t>https://artportalen.se/Sighting/135917649</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135917649</v>
+        <v>135917650</v>
       </c>
       <c r="B54" t="n">
         <v>79441</v>
@@ -6305,10 +6300,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>476998</v>
+        <v>476984</v>
       </c>
       <c r="R54" t="n">
-        <v>7044769</v>
+        <v>7044785</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6340,7 +6335,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6350,7 +6345,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:47</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6376,13 +6376,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917649</t>
+          <t>https://artportalen.se/Sighting/135917650</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135917650</v>
+        <v>135917651</v>
       </c>
       <c r="B55" t="n">
         <v>79441</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>476984</v>
+        <v>476955</v>
       </c>
       <c r="R55" t="n">
-        <v>7044785</v>
+        <v>7044809</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
@@ -6493,13 +6493,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917650</t>
+          <t>https://artportalen.se/Sighting/135917651</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135917651</v>
+        <v>135917653</v>
       </c>
       <c r="B56" t="n">
         <v>79441</v>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>476955</v>
+        <v>476754</v>
       </c>
       <c r="R56" t="n">
-        <v>7044809</v>
+        <v>7044898</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
@@ -6610,13 +6610,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917651</t>
+          <t>https://artportalen.se/Sighting/135917653</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135917653</v>
+        <v>135917655</v>
       </c>
       <c r="B57" t="n">
         <v>79441</v>
@@ -6651,10 +6651,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>476754</v>
+        <v>476732</v>
       </c>
       <c r="R57" t="n">
-        <v>7044898</v>
+        <v>7044931</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
@@ -6727,13 +6727,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917653</t>
+          <t>https://artportalen.se/Sighting/135917655</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135917655</v>
+        <v>135917663</v>
       </c>
       <c r="B58" t="n">
         <v>79441</v>
@@ -6768,10 +6768,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>476732</v>
+        <v>476740</v>
       </c>
       <c r="R58" t="n">
-        <v>7044931</v>
+        <v>7044997</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
@@ -6844,13 +6844,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917655</t>
+          <t>https://artportalen.se/Sighting/135917663</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135917663</v>
+        <v>135917664</v>
       </c>
       <c r="B59" t="n">
         <v>79441</v>
@@ -6885,10 +6885,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>476740</v>
+        <v>476718</v>
       </c>
       <c r="R59" t="n">
-        <v>7044997</v>
+        <v>7044987</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6961,13 +6961,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917663</t>
+          <t>https://artportalen.se/Sighting/135917664</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135917664</v>
+        <v>135917666</v>
       </c>
       <c r="B60" t="n">
         <v>79441</v>
@@ -7002,10 +7002,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>476718</v>
+        <v>476713</v>
       </c>
       <c r="R60" t="n">
-        <v>7044987</v>
+        <v>7044947</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
@@ -7078,13 +7078,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917664</t>
+          <t>https://artportalen.se/Sighting/135917666</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135917666</v>
+        <v>135944159</v>
       </c>
       <c r="B61" t="n">
         <v>79441</v>
@@ -7115,14 +7115,14 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>476713</v>
+        <v>476903</v>
       </c>
       <c r="R61" t="n">
-        <v>7044947</v>
+        <v>7044693</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7152,24 +7152,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>19:07</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>19:07</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7184,24 +7169,24 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917666</t>
+          <t>https://artportalen.se/Sighting/135944159</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135944159</v>
+        <v>135944161</v>
       </c>
       <c r="B62" t="n">
         <v>79441</v>
@@ -7236,10 +7221,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>476903</v>
+        <v>476884</v>
       </c>
       <c r="R62" t="n">
-        <v>7044693</v>
+        <v>7044699</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7297,13 +7282,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944159</t>
+          <t>https://artportalen.se/Sighting/135944161</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135944161</v>
+        <v>135944164</v>
       </c>
       <c r="B63" t="n">
         <v>79441</v>
@@ -7338,10 +7323,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>476884</v>
+        <v>476994</v>
       </c>
       <c r="R63" t="n">
-        <v>7044699</v>
+        <v>7044204</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7399,13 +7384,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944161</t>
+          <t>https://artportalen.se/Sighting/135944164</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135944164</v>
+        <v>135944167</v>
       </c>
       <c r="B64" t="n">
         <v>79441</v>
@@ -7440,10 +7425,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>476994</v>
+        <v>476812</v>
       </c>
       <c r="R64" t="n">
-        <v>7044204</v>
+        <v>7044014</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7501,13 +7486,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944164</t>
+          <t>https://artportalen.se/Sighting/135944167</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135944167</v>
+        <v>135944170</v>
       </c>
       <c r="B65" t="n">
         <v>79441</v>
@@ -7542,10 +7527,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>476812</v>
+        <v>476970</v>
       </c>
       <c r="R65" t="n">
-        <v>7044014</v>
+        <v>7044589</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7603,13 +7588,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944167</t>
+          <t>https://artportalen.se/Sighting/135944170</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135944170</v>
+        <v>135944172</v>
       </c>
       <c r="B66" t="n">
         <v>79441</v>
@@ -7644,10 +7629,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>476970</v>
+        <v>476774</v>
       </c>
       <c r="R66" t="n">
-        <v>7044589</v>
+        <v>7044740</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7705,13 +7690,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944170</t>
+          <t>https://artportalen.se/Sighting/135944172</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135944172</v>
+        <v>135944187</v>
       </c>
       <c r="B67" t="n">
         <v>79441</v>
@@ -7746,10 +7731,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>476774</v>
+        <v>477006</v>
       </c>
       <c r="R67" t="n">
-        <v>7044740</v>
+        <v>7044331</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7807,13 +7792,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944172</t>
+          <t>https://artportalen.se/Sighting/135944187</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135944187</v>
+        <v>135944189</v>
       </c>
       <c r="B68" t="n">
         <v>79441</v>
@@ -7848,10 +7833,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>477006</v>
+        <v>476866</v>
       </c>
       <c r="R68" t="n">
-        <v>7044331</v>
+        <v>7044714</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7909,13 +7894,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944187</t>
+          <t>https://artportalen.se/Sighting/135944189</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135944189</v>
+        <v>135944190</v>
       </c>
       <c r="B69" t="n">
         <v>79441</v>
@@ -7950,10 +7935,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>476866</v>
+        <v>477001</v>
       </c>
       <c r="R69" t="n">
-        <v>7044714</v>
+        <v>7044318</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8011,13 +7996,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944189</t>
+          <t>https://artportalen.se/Sighting/135944190</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135944190</v>
+        <v>135944196</v>
       </c>
       <c r="B70" t="n">
         <v>79441</v>
@@ -8052,10 +8037,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>477001</v>
+        <v>476973</v>
       </c>
       <c r="R70" t="n">
-        <v>7044318</v>
+        <v>7044526</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8113,13 +8098,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944190</t>
+          <t>https://artportalen.se/Sighting/135944196</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135944196</v>
+        <v>135944199</v>
       </c>
       <c r="B71" t="n">
         <v>79441</v>
@@ -8154,10 +8139,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>476973</v>
+        <v>476983</v>
       </c>
       <c r="R71" t="n">
-        <v>7044526</v>
+        <v>7044506</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8215,13 +8200,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944196</t>
+          <t>https://artportalen.se/Sighting/135944199</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135944199</v>
+        <v>135944202</v>
       </c>
       <c r="B72" t="n">
         <v>79441</v>
@@ -8256,10 +8241,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>476983</v>
+        <v>476972</v>
       </c>
       <c r="R72" t="n">
-        <v>7044506</v>
+        <v>7044511</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8317,13 +8302,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944199</t>
+          <t>https://artportalen.se/Sighting/135944202</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135944202</v>
+        <v>135945091</v>
       </c>
       <c r="B73" t="n">
         <v>79441</v>
@@ -8354,14 +8339,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Lundsjön, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>476972</v>
+        <v>476826</v>
       </c>
       <c r="R73" t="n">
-        <v>7044511</v>
+        <v>7044762</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8408,24 +8393,24 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944202</t>
+          <t>https://artportalen.se/Sighting/135945091</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135945091</v>
+        <v>135945092</v>
       </c>
       <c r="B74" t="n">
         <v>79441</v>
@@ -8460,10 +8445,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>476826</v>
+        <v>476931</v>
       </c>
       <c r="R74" t="n">
-        <v>7044762</v>
+        <v>7044326</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8521,51 +8506,51 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945091</t>
+          <t>https://artportalen.se/Sighting/135945092</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135945092</v>
+        <v>135888499</v>
       </c>
       <c r="B75" t="n">
-        <v>79441</v>
+        <v>80060</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>476931</v>
+        <v>476772</v>
       </c>
       <c r="R75" t="n">
-        <v>7044326</v>
+        <v>7044578</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8595,9 +8580,24 @@
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På brandstubbe.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8612,27 +8612,27 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945092</t>
+          <t>https://artportalen.se/Sighting/135888499</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135888499</v>
+        <v>135888120</v>
       </c>
       <c r="B76" t="n">
-        <v>80060</v>
+        <v>80556</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8640,21 +8640,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8664,10 +8664,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>476772</v>
+        <v>476815</v>
       </c>
       <c r="R76" t="n">
-        <v>7044578</v>
+        <v>7044589</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8709,12 +8709,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>På brandstubbe.</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8740,13 +8735,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888499</t>
+          <t>https://artportalen.se/Sighting/135888120</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135888120</v>
+        <v>135917620</v>
       </c>
       <c r="B77" t="n">
         <v>80556</v>
@@ -8777,14 +8772,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>476815</v>
+        <v>476796</v>
       </c>
       <c r="R77" t="n">
-        <v>7044589</v>
+        <v>7044305</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8816,7 +8811,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8826,7 +8821,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8841,24 +8836,24 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888120</t>
+          <t>https://artportalen.se/Sighting/135917620</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135917620</v>
+        <v>135917631</v>
       </c>
       <c r="B78" t="n">
         <v>80556</v>
@@ -8893,10 +8888,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>476796</v>
+        <v>476919</v>
       </c>
       <c r="R78" t="n">
-        <v>7044305</v>
+        <v>7044298</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8928,7 +8923,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8938,7 +8933,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8964,13 +8959,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917620</t>
+          <t>https://artportalen.se/Sighting/135917631</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135917631</v>
+        <v>135945085</v>
       </c>
       <c r="B79" t="n">
         <v>80556</v>
@@ -9005,10 +9000,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>476919</v>
+        <v>476913</v>
       </c>
       <c r="R79" t="n">
-        <v>7044298</v>
+        <v>7044303</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9038,19 +9033,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>17:06</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>17:06</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9076,13 +9061,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917631</t>
+          <t>https://artportalen.se/Sighting/135945085</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135945085</v>
+        <v>135945086</v>
       </c>
       <c r="B80" t="n">
         <v>80556</v>
@@ -9117,10 +9102,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>476913</v>
+        <v>476876</v>
       </c>
       <c r="R80" t="n">
-        <v>7044303</v>
+        <v>7044333</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9178,13 +9163,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945085</t>
+          <t>https://artportalen.se/Sighting/135945086</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135945086</v>
+        <v>135945087</v>
       </c>
       <c r="B81" t="n">
         <v>80556</v>
@@ -9219,10 +9204,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>476876</v>
+        <v>476931</v>
       </c>
       <c r="R81" t="n">
-        <v>7044333</v>
+        <v>7044324</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9280,13 +9265,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945086</t>
+          <t>https://artportalen.se/Sighting/135945087</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135945087</v>
+        <v>135945088</v>
       </c>
       <c r="B82" t="n">
         <v>80556</v>
@@ -9321,10 +9306,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>476931</v>
+        <v>476913</v>
       </c>
       <c r="R82" t="n">
-        <v>7044324</v>
+        <v>7044401</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9382,13 +9367,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945087</t>
+          <t>https://artportalen.se/Sighting/135945088</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135945088</v>
+        <v>135945089</v>
       </c>
       <c r="B83" t="n">
         <v>80556</v>
@@ -9423,10 +9408,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>476913</v>
+        <v>476929</v>
       </c>
       <c r="R83" t="n">
-        <v>7044401</v>
+        <v>7044362</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9484,38 +9469,38 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945088</t>
+          <t>https://artportalen.se/Sighting/135945089</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135945089</v>
+        <v>135945094</v>
       </c>
       <c r="B84" t="n">
-        <v>80556</v>
+        <v>79697</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9525,10 +9510,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>476929</v>
+        <v>476926</v>
       </c>
       <c r="R84" t="n">
-        <v>7044362</v>
+        <v>7044300</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9586,16 +9571,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945089</t>
+          <t>https://artportalen.se/Sighting/135945094</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135945094</v>
+        <v>113026760</v>
       </c>
       <c r="B85" t="n">
-        <v>79697</v>
+        <v>80461</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9603,34 +9588,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6459</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Långan-Tornäs, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>476926</v>
+        <v>476908</v>
       </c>
       <c r="R85" t="n">
-        <v>7044300</v>
+        <v>7044403</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9657,12 +9642,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9677,27 +9662,27 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945094</t>
+          <t>https://artportalen.se/Sighting/113026760</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>113026760</v>
+        <v>135888337</v>
       </c>
       <c r="B86" t="n">
-        <v>80461</v>
+        <v>80561</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9725,14 +9710,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>476908</v>
+        <v>476772</v>
       </c>
       <c r="R86" t="n">
-        <v>7044403</v>
+        <v>7044582</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9759,12 +9744,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9779,24 +9774,24 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026760</t>
+          <t>https://artportalen.se/Sighting/135888337</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135888337</v>
+        <v>135888567</v>
       </c>
       <c r="B87" t="n">
         <v>80561</v>
@@ -9831,10 +9826,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>476772</v>
+        <v>476766</v>
       </c>
       <c r="R87" t="n">
-        <v>7044582</v>
+        <v>7044606</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9866,7 +9861,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9876,7 +9871,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9902,13 +9897,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888337</t>
+          <t>https://artportalen.se/Sighting/135888567</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135888567</v>
+        <v>135889256</v>
       </c>
       <c r="B88" t="n">
         <v>80561</v>
@@ -9943,10 +9938,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>476766</v>
+        <v>476783</v>
       </c>
       <c r="R88" t="n">
-        <v>7044606</v>
+        <v>7044546</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9978,7 +9973,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -9988,7 +9983,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10014,13 +10009,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888567</t>
+          <t>https://artportalen.se/Sighting/135889256</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135889256</v>
+        <v>135890496</v>
       </c>
       <c r="B89" t="n">
         <v>80561</v>
@@ -10055,10 +10050,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>476783</v>
+        <v>476934</v>
       </c>
       <c r="R89" t="n">
-        <v>7044546</v>
+        <v>7044411</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10090,7 +10085,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10100,7 +10095,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10126,13 +10121,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889256</t>
+          <t>https://artportalen.se/Sighting/135890496</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135890496</v>
+        <v>135917621</v>
       </c>
       <c r="B90" t="n">
         <v>80561</v>
@@ -10163,14 +10158,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>476934</v>
+        <v>476796</v>
       </c>
       <c r="R90" t="n">
-        <v>7044411</v>
+        <v>7044304</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10202,7 +10197,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10212,7 +10207,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10227,27 +10222,27 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890496</t>
+          <t>https://artportalen.se/Sighting/135917621</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135917621</v>
+        <v>135888326</v>
       </c>
       <c r="B91" t="n">
-        <v>80561</v>
+        <v>80567</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10255,34 +10250,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6462</v>
+        <v>6463</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>476796</v>
+        <v>476767</v>
       </c>
       <c r="R91" t="n">
-        <v>7044304</v>
+        <v>7044584</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10314,7 +10309,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10324,7 +10319,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10339,24 +10334,24 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917621</t>
+          <t>https://artportalen.se/Sighting/135888326</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135888326</v>
+        <v>135945093</v>
       </c>
       <c r="B92" t="n">
         <v>80567</v>
@@ -10387,14 +10382,14 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>476767</v>
+        <v>476922</v>
       </c>
       <c r="R92" t="n">
-        <v>7044584</v>
+        <v>7044397</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10424,19 +10419,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>15:03</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>15:03</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10451,27 +10436,27 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888326</t>
+          <t>https://artportalen.se/Sighting/135945093</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135945093</v>
+        <v>135888134</v>
       </c>
       <c r="B93" t="n">
-        <v>80567</v>
+        <v>80568</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10479,34 +10464,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6463</v>
+        <v>6464</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>476922</v>
+        <v>476814</v>
       </c>
       <c r="R93" t="n">
-        <v>7044397</v>
+        <v>7044588</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10536,9 +10521,19 @@
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10553,24 +10548,24 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945093</t>
+          <t>https://artportalen.se/Sighting/135888134</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135888134</v>
+        <v>135944177</v>
       </c>
       <c r="B94" t="n">
         <v>80568</v>
@@ -10601,14 +10596,14 @@
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>476814</v>
+        <v>476994</v>
       </c>
       <c r="R94" t="n">
-        <v>7044588</v>
+        <v>7044300</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10638,19 +10633,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>14:58</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>14:58</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10665,27 +10650,27 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888134</t>
+          <t>https://artportalen.se/Sighting/135944177</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135944177</v>
+        <v>135888984</v>
       </c>
       <c r="B95" t="n">
-        <v>80568</v>
+        <v>57977</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10693,34 +10678,39 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lundsjön, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>476994</v>
+        <v>476754</v>
       </c>
       <c r="R95" t="n">
-        <v>7044300</v>
+        <v>7044651</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10750,9 +10740,24 @@
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Grovt bearbetad granhögstubbe</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10767,24 +10772,24 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944177</t>
+          <t>https://artportalen.se/Sighting/135888984</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135888984</v>
+        <v>135944169</v>
       </c>
       <c r="B96" t="n">
         <v>57977</v>
@@ -10815,19 +10820,19 @@
       <c r="I96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>476754</v>
+        <v>476883</v>
       </c>
       <c r="R96" t="n">
-        <v>7044651</v>
+        <v>7044170</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10857,24 +10862,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Grovt bearbetad granhögstubbe</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10889,44 +10879,44 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888984</t>
+          <t>https://artportalen.se/Sighting/135944169</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135944169</v>
+        <v>135888059</v>
       </c>
       <c r="B97" t="n">
-        <v>57977</v>
+        <v>57980</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10937,19 +10927,19 @@
       <c r="I97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lundsjön, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>476883</v>
+        <v>476798</v>
       </c>
       <c r="R97" t="n">
-        <v>7044170</v>
+        <v>7044601</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10979,9 +10969,24 @@
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Barkfläkt låga</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10996,24 +11001,24 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944169</t>
+          <t>https://artportalen.se/Sighting/135888059</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135888059</v>
+        <v>135888595</v>
       </c>
       <c r="B98" t="n">
         <v>57980</v>
@@ -11053,10 +11058,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>476798</v>
+        <v>476761</v>
       </c>
       <c r="R98" t="n">
-        <v>7044601</v>
+        <v>7044604</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11088,7 +11093,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11098,12 +11103,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>Barkfläkt låga</t>
+          <t>Barkfläkta granar</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11129,13 +11134,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888059</t>
+          <t>https://artportalen.se/Sighting/135888595</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135888595</v>
+        <v>135888744</v>
       </c>
       <c r="B99" t="n">
         <v>57980</v>
@@ -11166,7 +11171,7 @@
       <c r="I99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11175,10 +11180,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>476761</v>
+        <v>476766</v>
       </c>
       <c r="R99" t="n">
-        <v>7044604</v>
+        <v>7044622</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11210,7 +11215,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11220,12 +11225,12 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>Barkfläkta granar</t>
+          <t>Skalad klen gran.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11251,13 +11256,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888595</t>
+          <t>https://artportalen.se/Sighting/135888744</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135888744</v>
+        <v>135888896</v>
       </c>
       <c r="B100" t="n">
         <v>57980</v>
@@ -11297,10 +11302,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>476766</v>
+        <v>476754</v>
       </c>
       <c r="R100" t="n">
-        <v>7044622</v>
+        <v>7044651</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11332,7 +11337,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11342,12 +11347,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Skalad klen gran.</t>
+          <t>Barkfläkt och ringhackad gran</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11373,13 +11378,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888744</t>
+          <t>https://artportalen.se/Sighting/135888896</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135888896</v>
+        <v>135889188</v>
       </c>
       <c r="B101" t="n">
         <v>57980</v>
@@ -11410,7 +11415,7 @@
       <c r="I101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11419,10 +11424,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>476754</v>
+        <v>476747</v>
       </c>
       <c r="R101" t="n">
-        <v>7044651</v>
+        <v>7044563</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11454,7 +11459,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11464,12 +11469,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Barkfläkt och ringhackad gran</t>
+          <t>Barkfläkta granar</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11495,13 +11500,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888896</t>
+          <t>https://artportalen.se/Sighting/135889188</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135889188</v>
+        <v>135889243</v>
       </c>
       <c r="B102" t="n">
         <v>57980</v>
@@ -11541,10 +11546,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>476747</v>
+        <v>476778</v>
       </c>
       <c r="R102" t="n">
-        <v>7044563</v>
+        <v>7044558</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11576,7 +11581,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11586,12 +11591,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Barkfläkta granar</t>
+          <t>Flera barkskalade granar.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11617,13 +11622,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889188</t>
+          <t>https://artportalen.se/Sighting/135889243</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135889243</v>
+        <v>135889343</v>
       </c>
       <c r="B103" t="n">
         <v>57980</v>
@@ -11663,10 +11668,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>476778</v>
+        <v>476814</v>
       </c>
       <c r="R103" t="n">
-        <v>7044558</v>
+        <v>7044521</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11698,7 +11703,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11708,12 +11713,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Flera barkskalade granar.</t>
+          <t>Barkfläkt gran</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11739,13 +11744,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889243</t>
+          <t>https://artportalen.se/Sighting/135889343</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135889343</v>
+        <v>135890314</v>
       </c>
       <c r="B104" t="n">
         <v>57980</v>
@@ -11785,10 +11790,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>476814</v>
+        <v>476916</v>
       </c>
       <c r="R104" t="n">
-        <v>7044521</v>
+        <v>7044438</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11820,7 +11825,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11830,12 +11835,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Barkfläkt gran</t>
+          <t>Flera barkfläkta och skalade granar.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11861,13 +11866,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889343</t>
+          <t>https://artportalen.se/Sighting/135890314</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135890314</v>
+        <v>135917612</v>
       </c>
       <c r="B105" t="n">
         <v>57980</v>
@@ -11895,22 +11900,37 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>honfärgad</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>476916</v>
+        <v>476712</v>
       </c>
       <c r="R105" t="n">
-        <v>7044438</v>
+        <v>7044375</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11942,7 +11962,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11952,12 +11972,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Flera barkfläkta och skalade granar.</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11972,24 +11987,24 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890314</t>
+          <t>https://artportalen.se/Sighting/135917612</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135917612</v>
+        <v>135917618</v>
       </c>
       <c r="B106" t="n">
         <v>57980</v>
@@ -12044,10 +12059,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>476712</v>
+        <v>476783</v>
       </c>
       <c r="R106" t="n">
-        <v>7044375</v>
+        <v>7044308</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12079,7 +12094,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12089,7 +12104,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12115,13 +12130,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917612</t>
+          <t>https://artportalen.se/Sighting/135917618</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135917618</v>
+        <v>135917637</v>
       </c>
       <c r="B107" t="n">
         <v>57980</v>
@@ -12149,25 +12164,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="M107" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12176,10 +12176,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>476783</v>
+        <v>476966</v>
       </c>
       <c r="R107" t="n">
-        <v>7044308</v>
+        <v>7044462</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12211,7 +12211,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12221,7 +12221,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12247,13 +12252,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917618</t>
+          <t>https://artportalen.se/Sighting/135917637</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135917637</v>
+        <v>135917656</v>
       </c>
       <c r="B108" t="n">
         <v>57980</v>
@@ -12293,10 +12298,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>476966</v>
+        <v>476723</v>
       </c>
       <c r="R108" t="n">
-        <v>7044462</v>
+        <v>7044923</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12328,7 +12333,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12338,7 +12343,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:58</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr">
@@ -12369,13 +12374,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917637</t>
+          <t>https://artportalen.se/Sighting/135917656</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135917656</v>
+        <v>135917657</v>
       </c>
       <c r="B109" t="n">
         <v>57980</v>
@@ -12415,10 +12420,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>476723</v>
+        <v>476729</v>
       </c>
       <c r="R109" t="n">
-        <v>7044923</v>
+        <v>7044916</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12450,7 +12455,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12460,7 +12465,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>18:58</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr">
@@ -12491,13 +12496,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917656</t>
+          <t>https://artportalen.se/Sighting/135917657</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135917657</v>
+        <v>135917659</v>
       </c>
       <c r="B110" t="n">
         <v>57980</v>
@@ -12537,10 +12542,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>476729</v>
+        <v>476738</v>
       </c>
       <c r="R110" t="n">
-        <v>7044916</v>
+        <v>7044973</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12572,7 +12577,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12582,7 +12587,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
@@ -12613,13 +12618,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917657</t>
+          <t>https://artportalen.se/Sighting/135917659</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135917659</v>
+        <v>135917661</v>
       </c>
       <c r="B111" t="n">
         <v>57980</v>
@@ -12659,10 +12664,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>476738</v>
+        <v>476737</v>
       </c>
       <c r="R111" t="n">
-        <v>7044973</v>
+        <v>7044989</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12694,7 +12699,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12704,7 +12709,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
@@ -12735,13 +12740,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917659</t>
+          <t>https://artportalen.se/Sighting/135917661</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135917661</v>
+        <v>135917668</v>
       </c>
       <c r="B112" t="n">
         <v>57980</v>
@@ -12772,7 +12777,7 @@
       <c r="I112" t="inlineStr"/>
       <c r="M112" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -12781,10 +12786,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>476737</v>
+        <v>476706</v>
       </c>
       <c r="R112" t="n">
-        <v>7044989</v>
+        <v>7044899</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12816,7 +12821,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12826,12 +12831,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12857,13 +12862,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917661</t>
+          <t>https://artportalen.se/Sighting/135917668</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135917668</v>
+        <v>135917669</v>
       </c>
       <c r="B113" t="n">
         <v>57980</v>
@@ -12903,10 +12908,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>476706</v>
+        <v>476694</v>
       </c>
       <c r="R113" t="n">
-        <v>7044899</v>
+        <v>7044903</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12938,7 +12943,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12948,7 +12953,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
@@ -12979,13 +12984,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917668</t>
+          <t>https://artportalen.se/Sighting/135917669</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135917669</v>
+        <v>135944193</v>
       </c>
       <c r="B114" t="n">
         <v>57980</v>
@@ -13016,19 +13021,19 @@
       <c r="I114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>476694</v>
+        <v>476745</v>
       </c>
       <c r="R114" t="n">
-        <v>7044903</v>
+        <v>7044859</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13058,24 +13063,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13090,24 +13080,24 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917669</t>
+          <t>https://artportalen.se/Sighting/135944193</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135944193</v>
+        <v>135945069</v>
       </c>
       <c r="B115" t="n">
         <v>57980</v>
@@ -13136,21 +13126,24 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Lundsjön, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>476745</v>
+        <v>476723</v>
       </c>
       <c r="R115" t="n">
-        <v>7044859</v>
+        <v>7044873</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13185,6 +13178,11 @@
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -13197,24 +13195,24 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944193</t>
+          <t>https://artportalen.se/Sighting/135945069</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135945069</v>
+        <v>135945070</v>
       </c>
       <c r="B116" t="n">
         <v>57980</v>
@@ -13257,10 +13255,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>476723</v>
+        <v>476744</v>
       </c>
       <c r="R116" t="n">
-        <v>7044873</v>
+        <v>7044833</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13297,7 +13295,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13323,13 +13321,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945069</t>
+          <t>https://artportalen.se/Sighting/135945070</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135945070</v>
+        <v>135945071</v>
       </c>
       <c r="B117" t="n">
         <v>57980</v>
@@ -13372,10 +13370,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>476744</v>
+        <v>476739</v>
       </c>
       <c r="R117" t="n">
-        <v>7044833</v>
+        <v>7044860</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13438,13 +13436,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945070</t>
+          <t>https://artportalen.se/Sighting/135945071</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135945071</v>
+        <v>135945072</v>
       </c>
       <c r="B118" t="n">
         <v>57980</v>
@@ -13487,10 +13485,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>476739</v>
+        <v>476733</v>
       </c>
       <c r="R118" t="n">
-        <v>7044860</v>
+        <v>7044869</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13553,13 +13551,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945071</t>
+          <t>https://artportalen.se/Sighting/135945072</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135945072</v>
+        <v>135945073</v>
       </c>
       <c r="B119" t="n">
         <v>57980</v>
@@ -13602,10 +13600,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>476733</v>
+        <v>476736</v>
       </c>
       <c r="R119" t="n">
-        <v>7044869</v>
+        <v>7044864</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13668,13 +13666,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945072</t>
+          <t>https://artportalen.se/Sighting/135945073</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135945073</v>
+        <v>135945074</v>
       </c>
       <c r="B120" t="n">
         <v>57980</v>
@@ -13707,7 +13705,7 @@
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -13717,10 +13715,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>476736</v>
+        <v>476757</v>
       </c>
       <c r="R120" t="n">
-        <v>7044864</v>
+        <v>7044830</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13757,7 +13755,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13783,13 +13781,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945073</t>
+          <t>https://artportalen.se/Sighting/135945074</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135945074</v>
+        <v>135945075</v>
       </c>
       <c r="B121" t="n">
         <v>57980</v>
@@ -13832,10 +13830,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>476757</v>
+        <v>476759</v>
       </c>
       <c r="R121" t="n">
-        <v>7044830</v>
+        <v>7044831</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13898,13 +13896,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945074</t>
+          <t>https://artportalen.se/Sighting/135945075</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135945075</v>
+        <v>135945076</v>
       </c>
       <c r="B122" t="n">
         <v>57980</v>
@@ -13937,7 +13935,7 @@
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
@@ -13947,10 +13945,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>476759</v>
+        <v>476789</v>
       </c>
       <c r="R122" t="n">
-        <v>7044831</v>
+        <v>7044837</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13987,7 +13985,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>Äldre ringhack på gran</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14013,33 +14011,33 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945075</t>
+          <t>https://artportalen.se/Sighting/135945076</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135945076</v>
+        <v>135917641</v>
       </c>
       <c r="B123" t="n">
-        <v>57980</v>
+        <v>57158</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -14048,24 +14046,16 @@
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>476789</v>
+        <v>476955</v>
       </c>
       <c r="R123" t="n">
-        <v>7044837</v>
+        <v>7044640</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14095,14 +14085,19 @@
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14128,51 +14123,60 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945076</t>
+          <t>https://artportalen.se/Sighting/135917641</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135917641</v>
+        <v>135888587</v>
       </c>
       <c r="B124" t="n">
-        <v>57158</v>
+        <v>58141</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>476955</v>
+        <v>476762</v>
       </c>
       <c r="R124" t="n">
-        <v>7044640</v>
+        <v>7044603</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14204,7 +14208,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14214,7 +14218,12 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>15:13</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Par i permanent revir?</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14229,24 +14238,24 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917641</t>
+          <t>https://artportalen.se/Sighting/135888587</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135888587</v>
+        <v>135889674</v>
       </c>
       <c r="B125" t="n">
         <v>58141</v>
@@ -14290,10 +14299,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>476762</v>
+        <v>476881</v>
       </c>
       <c r="R125" t="n">
-        <v>7044603</v>
+        <v>7044438</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14325,7 +14334,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14335,12 +14344,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>15:13</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Par i permanent revir?</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14366,13 +14370,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888587</t>
+          <t>https://artportalen.se/Sighting/135889674</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135889674</v>
+        <v>135945077</v>
       </c>
       <c r="B126" t="n">
         <v>58141</v>
@@ -14405,21 +14409,24 @@
           <t>2</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>476881</v>
+        <v>476862</v>
       </c>
       <c r="R126" t="n">
-        <v>7044438</v>
+        <v>7044428</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14449,19 +14456,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14476,74 +14473,62 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889674</t>
+          <t>https://artportalen.se/Sighting/135945077</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>135945077</v>
+        <v>135888848</v>
       </c>
       <c r="B127" t="n">
-        <v>58141</v>
+        <v>99278</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>103021</v>
+        <v>219811</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>476862</v>
+        <v>476754</v>
       </c>
       <c r="R127" t="n">
-        <v>7044428</v>
+        <v>7044651</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14573,9 +14558,19 @@
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14590,27 +14585,27 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135945077</t>
+          <t>https://artportalen.se/Sighting/135888848</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>135888848</v>
+        <v>135888822</v>
       </c>
       <c r="B128" t="n">
-        <v>99278</v>
+        <v>99300</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14618,21 +14613,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219811</v>
+        <v>219847</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14677,7 +14672,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14687,7 +14682,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14713,16 +14708,16 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888848</t>
+          <t>https://artportalen.se/Sighting/135888822</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>135888822</v>
+        <v>135944179</v>
       </c>
       <c r="B129" t="n">
-        <v>99300</v>
+        <v>108294</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14730,34 +14725,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219847</v>
+        <v>220083</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>476754</v>
+        <v>476851</v>
       </c>
       <c r="R129" t="n">
-        <v>7044651</v>
+        <v>7044079</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14787,19 +14782,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>15:23</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>15:23</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14814,27 +14799,27 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888822</t>
+          <t>https://artportalen.se/Sighting/135944179</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>135944179</v>
+        <v>135888619</v>
       </c>
       <c r="B130" t="n">
-        <v>108294</v>
+        <v>99180</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14842,37 +14827,42 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220083</v>
+        <v>220093</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Lundsjön, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>476851</v>
+        <v>476761</v>
       </c>
       <c r="R130" t="n">
-        <v>7044079</v>
+        <v>7044604</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14899,9 +14889,19 @@
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14916,24 +14916,24 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944179</t>
+          <t>https://artportalen.se/Sighting/135888619</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>135888619</v>
+        <v>135889613</v>
       </c>
       <c r="B131" t="n">
         <v>99180</v>
@@ -14962,24 +14962,19 @@
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>476761</v>
+        <v>476865</v>
       </c>
       <c r="R131" t="n">
-        <v>7044604</v>
+        <v>7044458</v>
       </c>
       <c r="S131" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15008,7 +15003,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15018,7 +15013,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15044,51 +15039,60 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888619</t>
+          <t>https://artportalen.se/Sighting/135889613</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>135889613</v>
+        <v>135889209</v>
       </c>
       <c r="B132" t="n">
-        <v>99180</v>
+        <v>99276</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220093</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>476865</v>
+        <v>476778</v>
       </c>
       <c r="R132" t="n">
-        <v>7044458</v>
+        <v>7044558</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15120,7 +15124,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15130,7 +15134,12 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Många i blom</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15156,13 +15165,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889613</t>
+          <t>https://artportalen.se/Sighting/135889209</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>135889209</v>
+        <v>135944165</v>
       </c>
       <c r="B133" t="n">
         <v>99276</v>
@@ -15192,24 +15201,31 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>500</t>
+          <t>26</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>476778</v>
+        <v>476752</v>
       </c>
       <c r="R133" t="n">
-        <v>7044558</v>
+        <v>7044025</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15239,110 +15255,94 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Många i blom</t>
-        </is>
-      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889209</t>
+          <t>https://artportalen.se/Sighting/135944165</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>135944165</v>
+        <v>135889164</v>
       </c>
       <c r="B134" t="n">
-        <v>99276</v>
+        <v>106398</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Lundsjön, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>476752</v>
+        <v>476747</v>
       </c>
       <c r="R134" t="n">
-        <v>7044025</v>
+        <v>7044563</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15372,42 +15372,51 @@
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
       <c r="AE134" t="b">
         <v>0</v>
       </c>
-      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944165</t>
+          <t>https://artportalen.se/Sighting/135889164</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>135889164</v>
+        <v>135944158</v>
       </c>
       <c r="B135" t="n">
         <v>106398</v>
@@ -15435,31 +15444,17 @@
           <t>(L.) A. Gray</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>476747</v>
+        <v>476700</v>
       </c>
       <c r="R135" t="n">
-        <v>7044563</v>
+        <v>7044045</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15489,19 +15484,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>15:46</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15516,24 +15501,24 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889164</t>
+          <t>https://artportalen.se/Sighting/135944158</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>135944158</v>
+        <v>135944178</v>
       </c>
       <c r="B136" t="n">
         <v>106398</v>
@@ -15568,10 +15553,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>476700</v>
+        <v>476751</v>
       </c>
       <c r="R136" t="n">
-        <v>7044045</v>
+        <v>7044021</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15629,13 +15614,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944158</t>
+          <t>https://artportalen.se/Sighting/135944178</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>135944178</v>
+        <v>135944184</v>
       </c>
       <c r="B137" t="n">
         <v>106398</v>
@@ -15670,10 +15655,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>476751</v>
+        <v>476732</v>
       </c>
       <c r="R137" t="n">
-        <v>7044021</v>
+        <v>7044080</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15731,16 +15716,16 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944178</t>
+          <t>https://artportalen.se/Sighting/135944184</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>135944184</v>
+        <v>113026767</v>
       </c>
       <c r="B138" t="n">
-        <v>106398</v>
+        <v>97983</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15748,34 +15733,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>221725</v>
+        <v>221945</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Lundsjön, Jmt</t>
+          <t>Långan-Tornäs, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>476732</v>
+        <v>476711</v>
       </c>
       <c r="R138" t="n">
-        <v>7044080</v>
+        <v>7044397</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15802,12 +15787,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15822,24 +15807,24 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>August Alvtegen</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944184</t>
+          <t>https://artportalen.se/Sighting/113026767</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>113026767</v>
+        <v>113026771</v>
       </c>
       <c r="B139" t="n">
         <v>97983</v>
@@ -15874,10 +15859,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>476711</v>
+        <v>476874</v>
       </c>
       <c r="R139" t="n">
-        <v>7044397</v>
+        <v>7044428</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15935,13 +15920,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026767</t>
+          <t>https://artportalen.se/Sighting/113026771</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>113026771</v>
+        <v>113026772</v>
       </c>
       <c r="B140" t="n">
         <v>97983</v>
@@ -15976,10 +15961,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>476874</v>
+        <v>476774</v>
       </c>
       <c r="R140" t="n">
-        <v>7044428</v>
+        <v>7044383</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16037,16 +16022,16 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026771</t>
+          <t>https://artportalen.se/Sighting/113026772</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>113026772</v>
+        <v>135888627</v>
       </c>
       <c r="B141" t="n">
-        <v>97983</v>
+        <v>99298</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16054,34 +16039,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>221945</v>
+        <v>221952</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Långan-Tornäs, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>476774</v>
+        <v>476761</v>
       </c>
       <c r="R141" t="n">
-        <v>7044383</v>
+        <v>7044604</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16108,12 +16093,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2023-10-16</t>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16128,24 +16123,24 @@
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>August Alvtegen</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113026772</t>
+          <t>https://artportalen.se/Sighting/135888627</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>135888627</v>
+        <v>135889141</v>
       </c>
       <c r="B142" t="n">
         <v>99298</v>
@@ -16180,10 +16175,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>476761</v>
+        <v>476694</v>
       </c>
       <c r="R142" t="n">
-        <v>7044604</v>
+        <v>7044597</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16215,7 +16210,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16225,7 +16220,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16251,13 +16246,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888627</t>
+          <t>https://artportalen.se/Sighting/135889141</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>135889141</v>
+        <v>135889396</v>
       </c>
       <c r="B143" t="n">
         <v>99298</v>
@@ -16292,10 +16287,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>476694</v>
+        <v>476814</v>
       </c>
       <c r="R143" t="n">
-        <v>7044597</v>
+        <v>7044521</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16327,7 +16322,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16337,7 +16332,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16363,13 +16358,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889141</t>
+          <t>https://artportalen.se/Sighting/135889396</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>135889396</v>
+        <v>135890358</v>
       </c>
       <c r="B144" t="n">
         <v>99298</v>
@@ -16397,17 +16392,26 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>476814</v>
+        <v>476916</v>
       </c>
       <c r="R144" t="n">
-        <v>7044521</v>
+        <v>7044438</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16439,7 +16443,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16449,7 +16453,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16475,13 +16479,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889396</t>
+          <t>https://artportalen.se/Sighting/135890358</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>135890358</v>
+        <v>135917602</v>
       </c>
       <c r="B145" t="n">
         <v>99298</v>
@@ -16509,26 +16513,17 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön N, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>476916</v>
+        <v>476830</v>
       </c>
       <c r="R145" t="n">
-        <v>7044438</v>
+        <v>7044560</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16560,7 +16555,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16570,7 +16565,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16585,24 +16580,24 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135890358</t>
+          <t>https://artportalen.se/Sighting/135917602</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>135917602</v>
+        <v>135944160</v>
       </c>
       <c r="B146" t="n">
         <v>99298</v>
@@ -16633,14 +16628,14 @@
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Lundsjön N, Jmt</t>
+          <t>Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>476830</v>
+        <v>476727</v>
       </c>
       <c r="R146" t="n">
-        <v>7044560</v>
+        <v>7044153</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16670,19 +16665,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z146" t="inlineStr">
-        <is>
-          <t>14:47</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB146" t="inlineStr">
-        <is>
-          <t>14:47</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16697,24 +16682,24 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135917602</t>
+          <t>https://artportalen.se/Sighting/135944160</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>135944160</v>
+        <v>135944191</v>
       </c>
       <c r="B147" t="n">
         <v>99298</v>
@@ -16749,10 +16734,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>476727</v>
+        <v>476994</v>
       </c>
       <c r="R147" t="n">
-        <v>7044153</v>
+        <v>7044206</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16810,13 +16795,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944160</t>
+          <t>https://artportalen.se/Sighting/135944191</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>135944191</v>
+        <v>135944195</v>
       </c>
       <c r="B148" t="n">
         <v>99298</v>
@@ -16851,10 +16836,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>476994</v>
+        <v>476786</v>
       </c>
       <c r="R148" t="n">
-        <v>7044206</v>
+        <v>7044008</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16912,16 +16897,16 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944191</t>
+          <t>https://artportalen.se/Sighting/135944195</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>135944195</v>
+        <v>135888967</v>
       </c>
       <c r="B149" t="n">
-        <v>99298</v>
+        <v>99553</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16929,34 +16914,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>221952</v>
+        <v>222812</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Lundsjön, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>476786</v>
+        <v>476754</v>
       </c>
       <c r="R149" t="n">
-        <v>7044008</v>
+        <v>7044651</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16986,9 +16971,19 @@
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17003,27 +16998,27 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944195</t>
+          <t>https://artportalen.se/Sighting/135888967</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>135888967</v>
+        <v>135889868</v>
       </c>
       <c r="B150" t="n">
-        <v>99553</v>
+        <v>99082</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17031,16 +17026,16 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>222812</v>
+        <v>223049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -17055,10 +17050,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>476754</v>
+        <v>476906</v>
       </c>
       <c r="R150" t="n">
-        <v>7044651</v>
+        <v>7044422</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17090,7 +17085,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -17100,7 +17095,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17126,13 +17121,13 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135888967</t>
+          <t>https://artportalen.se/Sighting/135889868</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>135889868</v>
+        <v>135944198</v>
       </c>
       <c r="B151" t="n">
         <v>99082</v>
@@ -17163,14 +17158,14 @@
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>476906</v>
+        <v>476995</v>
       </c>
       <c r="R151" t="n">
-        <v>7044422</v>
+        <v>7044208</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17200,19 +17195,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>16:16</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17227,27 +17212,27 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135889868</t>
+          <t>https://artportalen.se/Sighting/135944198</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>135944198</v>
+        <v>135889874</v>
       </c>
       <c r="B152" t="n">
-        <v>99082</v>
+        <v>98327</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17255,34 +17240,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>223049</v>
+        <v>223358</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Lundsjön, Jmt</t>
+          <t>Storrönningen, Storrönningen, Jmt</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>476995</v>
+        <v>476902</v>
       </c>
       <c r="R152" t="n">
-        <v>7044208</v>
+        <v>7044424</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17312,9 +17297,19 @@
           <t>2026-08-14</t>
         </is>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17329,27 +17324,27 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135944198</t>
+          <t>https://artportalen.se/Sighting/135889874</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>135889874</v>
+        <v>135944188</v>
       </c>
       <c r="B153" t="n">
-        <v>98327</v>
+        <v>101375</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17357,34 +17352,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>223358</v>
+        <v>224885</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Storrönningen, Storrönningen, Jmt</t>
+          <t>Lundsjön, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>476902</v>
+        <v>476933</v>
       </c>
       <c r="R153" t="n">
-        <v>7044424</v>
+        <v>7044167</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17414,19 +17409,9 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>16:16</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17441,118 +17426,16 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135889874</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>135944188</v>
-      </c>
-      <c r="B154" t="n">
-        <v>101375</v>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E154" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>Lundsjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q154" t="n">
-        <v>476933</v>
-      </c>
-      <c r="R154" t="n">
-        <v>7044167</v>
-      </c>
-      <c r="S154" t="n">
-        <v>10</v>
-      </c>
-      <c r="T154" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>Aspås</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="AD154" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE154" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG154" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT154" t="inlineStr"/>
-      <c r="AW154" t="inlineStr">
-        <is>
-          <t>Britta Sterner</t>
-        </is>
-      </c>
-      <c r="AX154" t="inlineStr">
-        <is>
-          <t>Britta Sterner</t>
-        </is>
-      </c>
-      <c r="AY154" t="inlineStr"/>
-      <c r="AZ154" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135944188</t>
         </is>
@@ -17712,7 +17595,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31237-2026 artfynd.xlsx
+++ b/artfynd/A 31237-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890448</v>
       </c>
       <c r="B2" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135944192</v>
       </c>
       <c r="B3" t="n">
-        <v>89428</v>
+        <v>89430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135890254</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917629</v>
       </c>
       <c r="B5" t="n">
-        <v>92622</v>
+        <v>92637</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135888100</v>
       </c>
       <c r="B6" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917622</v>
       </c>
       <c r="B7" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135888945</v>
       </c>
       <c r="B9" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135889310</v>
       </c>
       <c r="B10" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135890261</v>
       </c>
       <c r="B11" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>135890410</v>
       </c>
       <c r="B12" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135890469</v>
       </c>
       <c r="B13" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135917603</v>
       </c>
       <c r="B14" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135917607</v>
       </c>
       <c r="B15" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135945068</v>
       </c>
       <c r="B16" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135945090</v>
       </c>
       <c r="B17" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>135890793</v>
       </c>
       <c r="B23" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135917639</v>
       </c>
       <c r="B24" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>135944181</v>
       </c>
       <c r="B25" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>135945080</v>
       </c>
       <c r="B26" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>135945081</v>
       </c>
       <c r="B27" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>135945082</v>
       </c>
       <c r="B28" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>135945083</v>
       </c>
       <c r="B29" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>135945084</v>
       </c>
       <c r="B30" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>135889516</v>
       </c>
       <c r="B31" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>135944174</v>
       </c>
       <c r="B32" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>135917605</v>
       </c>
       <c r="B33" t="n">
-        <v>92275</v>
+        <v>92289</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>135944194</v>
       </c>
       <c r="B34" t="n">
-        <v>92275</v>
+        <v>92289</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>135887935</v>
       </c>
       <c r="B35" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>135917600</v>
       </c>
       <c r="B36" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135917609</v>
       </c>
       <c r="B37" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>135917632</v>
       </c>
       <c r="B38" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>135944171</v>
       </c>
       <c r="B39" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135944197</v>
       </c>
       <c r="B40" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>135945066</v>
       </c>
       <c r="B41" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>135945067</v>
       </c>
       <c r="B42" t="n">
-        <v>89292</v>
+        <v>89294</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135887747</v>
       </c>
       <c r="B43" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>135890276</v>
       </c>
       <c r="B44" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135944200</v>
       </c>
       <c r="B45" t="n">
-        <v>92013</v>
+        <v>92027</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>135887305</v>
       </c>
       <c r="B48" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>135888884</v>
       </c>
       <c r="B49" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>135889085</v>
       </c>
       <c r="B50" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>135889333</v>
       </c>
       <c r="B51" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135917634</v>
       </c>
       <c r="B52" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135917649</v>
       </c>
       <c r="B53" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>135917650</v>
       </c>
       <c r="B54" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>135917651</v>
       </c>
       <c r="B55" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>135917653</v>
       </c>
       <c r="B56" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>135917655</v>
       </c>
       <c r="B57" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>135917663</v>
       </c>
       <c r="B58" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>135917664</v>
       </c>
       <c r="B59" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>135917666</v>
       </c>
       <c r="B60" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>135944159</v>
       </c>
       <c r="B61" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>135944161</v>
       </c>
       <c r="B62" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>135944164</v>
       </c>
       <c r="B63" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>135944167</v>
       </c>
       <c r="B64" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>135944170</v>
       </c>
       <c r="B65" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>135944172</v>
       </c>
       <c r="B66" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>135944187</v>
       </c>
       <c r="B67" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>135944189</v>
       </c>
       <c r="B68" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>135944190</v>
       </c>
       <c r="B69" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>135944196</v>
       </c>
       <c r="B70" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>135944199</v>
       </c>
       <c r="B71" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>135944202</v>
       </c>
       <c r="B72" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>135945091</v>
       </c>
       <c r="B73" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135945092</v>
       </c>
       <c r="B74" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>135888499</v>
       </c>
       <c r="B75" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>135888120</v>
       </c>
       <c r="B76" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>135917620</v>
       </c>
       <c r="B77" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>135917631</v>
       </c>
       <c r="B78" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>135945085</v>
       </c>
       <c r="B79" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>135945086</v>
       </c>
       <c r="B80" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>135945087</v>
       </c>
       <c r="B81" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>135945088</v>
       </c>
       <c r="B82" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>135945089</v>
       </c>
       <c r="B83" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>135945094</v>
       </c>
       <c r="B84" t="n">
-        <v>79697</v>
+        <v>79699</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>135888337</v>
       </c>
       <c r="B86" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>135888567</v>
       </c>
       <c r="B87" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>135889256</v>
       </c>
       <c r="B88" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>135890496</v>
       </c>
       <c r="B89" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>135917621</v>
       </c>
       <c r="B90" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>135888326</v>
       </c>
       <c r="B91" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>135945093</v>
       </c>
       <c r="B92" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>135888134</v>
       </c>
       <c r="B93" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>135944177</v>
       </c>
       <c r="B94" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>135888984</v>
       </c>
       <c r="B95" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>135944169</v>
       </c>
       <c r="B96" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>135888059</v>
       </c>
       <c r="B97" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>135888595</v>
       </c>
       <c r="B98" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>135888744</v>
       </c>
       <c r="B99" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>135888896</v>
       </c>
       <c r="B100" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>135889188</v>
       </c>
       <c r="B101" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>135889243</v>
       </c>
       <c r="B102" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>135889343</v>
       </c>
       <c r="B103" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>135890314</v>
       </c>
       <c r="B104" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>135917612</v>
       </c>
       <c r="B105" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>135917618</v>
       </c>
       <c r="B106" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>135917637</v>
       </c>
       <c r="B107" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>135917656</v>
       </c>
       <c r="B108" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>135917657</v>
       </c>
       <c r="B109" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>135917659</v>
       </c>
       <c r="B110" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>135917661</v>
       </c>
       <c r="B111" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>135917668</v>
       </c>
       <c r="B112" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>135917669</v>
       </c>
       <c r="B113" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>135944193</v>
       </c>
       <c r="B114" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>135945069</v>
       </c>
       <c r="B115" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>135945070</v>
       </c>
       <c r="B116" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>135945071</v>
       </c>
       <c r="B117" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>135945072</v>
       </c>
       <c r="B118" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>135945073</v>
       </c>
       <c r="B119" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>135945074</v>
       </c>
       <c r="B120" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>135945075</v>
       </c>
       <c r="B121" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>135945076</v>
       </c>
       <c r="B122" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>135917641</v>
       </c>
       <c r="B123" t="n">
-        <v>57158</v>
+        <v>57160</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>135888587</v>
       </c>
       <c r="B124" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>135889674</v>
       </c>
       <c r="B125" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>135945077</v>
       </c>
       <c r="B126" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>135888848</v>
       </c>
       <c r="B127" t="n">
-        <v>99278</v>
+        <v>99295</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>135888822</v>
       </c>
       <c r="B128" t="n">
-        <v>99300</v>
+        <v>99317</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>135944179</v>
       </c>
       <c r="B129" t="n">
-        <v>108294</v>
+        <v>108317</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>135888619</v>
       </c>
       <c r="B130" t="n">
-        <v>99180</v>
+        <v>99197</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>135889613</v>
       </c>
       <c r="B131" t="n">
-        <v>99180</v>
+        <v>99197</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>135889209</v>
       </c>
       <c r="B132" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>135944165</v>
       </c>
       <c r="B133" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>135889164</v>
       </c>
       <c r="B134" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>135944158</v>
       </c>
       <c r="B135" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>135944178</v>
       </c>
       <c r="B136" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>135944184</v>
       </c>
       <c r="B137" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>135888627</v>
       </c>
       <c r="B141" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>135889141</v>
       </c>
       <c r="B142" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>135889396</v>
       </c>
       <c r="B143" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>135890358</v>
       </c>
       <c r="B144" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>135917602</v>
       </c>
       <c r="B145" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>135944160</v>
       </c>
       <c r="B146" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>135944191</v>
       </c>
       <c r="B147" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>135944195</v>
       </c>
       <c r="B148" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>135888967</v>
       </c>
       <c r="B149" t="n">
-        <v>99553</v>
+        <v>99570</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>135889868</v>
       </c>
       <c r="B150" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>135944198</v>
       </c>
       <c r="B151" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>135889874</v>
       </c>
       <c r="B152" t="n">
-        <v>98327</v>
+        <v>98344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135944188</v>
       </c>
       <c r="B153" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 31237-2026 artfynd.xlsx
+++ b/artfynd/A 31237-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890448</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135944192</v>
       </c>
       <c r="B3" t="n">
-        <v>89430</v>
+        <v>89431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135890254</v>
       </c>
       <c r="B4" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917629</v>
       </c>
       <c r="B5" t="n">
-        <v>92637</v>
+        <v>92638</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135888100</v>
       </c>
       <c r="B6" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917622</v>
       </c>
       <c r="B7" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135888945</v>
       </c>
       <c r="B9" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135889310</v>
       </c>
       <c r="B10" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135890261</v>
       </c>
       <c r="B11" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>135890410</v>
       </c>
       <c r="B12" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135890469</v>
       </c>
       <c r="B13" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135917603</v>
       </c>
       <c r="B14" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135917607</v>
       </c>
       <c r="B15" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135945068</v>
       </c>
       <c r="B16" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135945090</v>
       </c>
       <c r="B17" t="n">
-        <v>92078</v>
+        <v>92079</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>135890793</v>
       </c>
       <c r="B23" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135917639</v>
       </c>
       <c r="B24" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>135944181</v>
       </c>
       <c r="B25" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>135945080</v>
       </c>
       <c r="B26" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>135945081</v>
       </c>
       <c r="B27" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>135945082</v>
       </c>
       <c r="B28" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>135945083</v>
       </c>
       <c r="B29" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>135945084</v>
       </c>
       <c r="B30" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>135889516</v>
       </c>
       <c r="B31" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>135944174</v>
       </c>
       <c r="B32" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>135917605</v>
       </c>
       <c r="B33" t="n">
-        <v>92289</v>
+        <v>92290</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>135944194</v>
       </c>
       <c r="B34" t="n">
-        <v>92289</v>
+        <v>92290</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>135887935</v>
       </c>
       <c r="B35" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>135917600</v>
       </c>
       <c r="B36" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135917609</v>
       </c>
       <c r="B37" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>135917632</v>
       </c>
       <c r="B38" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>135944171</v>
       </c>
       <c r="B39" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135944197</v>
       </c>
       <c r="B40" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>135945066</v>
       </c>
       <c r="B41" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>135945067</v>
       </c>
       <c r="B42" t="n">
-        <v>89294</v>
+        <v>89295</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135887747</v>
       </c>
       <c r="B43" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>135890276</v>
       </c>
       <c r="B44" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135944200</v>
       </c>
       <c r="B45" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>135887305</v>
       </c>
       <c r="B48" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>135888884</v>
       </c>
       <c r="B49" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>135889085</v>
       </c>
       <c r="B50" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>135889333</v>
       </c>
       <c r="B51" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135917634</v>
       </c>
       <c r="B52" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135917649</v>
       </c>
       <c r="B53" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>135917650</v>
       </c>
       <c r="B54" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>135917651</v>
       </c>
       <c r="B55" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>135917653</v>
       </c>
       <c r="B56" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>135917655</v>
       </c>
       <c r="B57" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>135917663</v>
       </c>
       <c r="B58" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>135917664</v>
       </c>
       <c r="B59" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>135917666</v>
       </c>
       <c r="B60" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>135944159</v>
       </c>
       <c r="B61" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>135944161</v>
       </c>
       <c r="B62" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>135944164</v>
       </c>
       <c r="B63" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>135944167</v>
       </c>
       <c r="B64" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>135944170</v>
       </c>
       <c r="B65" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>135944172</v>
       </c>
       <c r="B66" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>135944187</v>
       </c>
       <c r="B67" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>135944189</v>
       </c>
       <c r="B68" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>135944190</v>
       </c>
       <c r="B69" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>135944196</v>
       </c>
       <c r="B70" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>135944199</v>
       </c>
       <c r="B71" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>135944202</v>
       </c>
       <c r="B72" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>135945091</v>
       </c>
       <c r="B73" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135945092</v>
       </c>
       <c r="B74" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>135888499</v>
       </c>
       <c r="B75" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>135888120</v>
       </c>
       <c r="B76" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>135917620</v>
       </c>
       <c r="B77" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>135917631</v>
       </c>
       <c r="B78" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>135945085</v>
       </c>
       <c r="B79" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>135945086</v>
       </c>
       <c r="B80" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>135945087</v>
       </c>
       <c r="B81" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>135945088</v>
       </c>
       <c r="B82" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>135945089</v>
       </c>
       <c r="B83" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>135945094</v>
       </c>
       <c r="B84" t="n">
-        <v>79699</v>
+        <v>79700</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>135888337</v>
       </c>
       <c r="B86" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>135888567</v>
       </c>
       <c r="B87" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>135889256</v>
       </c>
       <c r="B88" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>135890496</v>
       </c>
       <c r="B89" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>135917621</v>
       </c>
       <c r="B90" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>135888326</v>
       </c>
       <c r="B91" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>135945093</v>
       </c>
       <c r="B92" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>135888134</v>
       </c>
       <c r="B93" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>135944177</v>
       </c>
       <c r="B94" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>135888848</v>
       </c>
       <c r="B127" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>135888822</v>
       </c>
       <c r="B128" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>135944179</v>
       </c>
       <c r="B129" t="n">
-        <v>108317</v>
+        <v>108319</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>135888619</v>
       </c>
       <c r="B130" t="n">
-        <v>99197</v>
+        <v>99198</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>135889613</v>
       </c>
       <c r="B131" t="n">
-        <v>99197</v>
+        <v>99198</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>135889209</v>
       </c>
       <c r="B132" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>135944165</v>
       </c>
       <c r="B133" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>135889164</v>
       </c>
       <c r="B134" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>135944158</v>
       </c>
       <c r="B135" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>135944178</v>
       </c>
       <c r="B136" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>135944184</v>
       </c>
       <c r="B137" t="n">
-        <v>106418</v>
+        <v>106420</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>135888627</v>
       </c>
       <c r="B141" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>135889141</v>
       </c>
       <c r="B142" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>135889396</v>
       </c>
       <c r="B143" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>135890358</v>
       </c>
       <c r="B144" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>135917602</v>
       </c>
       <c r="B145" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>135944160</v>
       </c>
       <c r="B146" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>135944191</v>
       </c>
       <c r="B147" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>135944195</v>
       </c>
       <c r="B148" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>135888967</v>
       </c>
       <c r="B149" t="n">
-        <v>99570</v>
+        <v>99571</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>135889868</v>
       </c>
       <c r="B150" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>135944198</v>
       </c>
       <c r="B151" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>135889874</v>
       </c>
       <c r="B152" t="n">
-        <v>98344</v>
+        <v>98345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135944188</v>
       </c>
       <c r="B153" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 31237-2026 artfynd.xlsx
+++ b/artfynd/A 31237-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890448</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135944192</v>
       </c>
       <c r="B3" t="n">
-        <v>89431</v>
+        <v>89432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135890254</v>
       </c>
       <c r="B4" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917629</v>
       </c>
       <c r="B5" t="n">
-        <v>92638</v>
+        <v>92639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135888100</v>
       </c>
       <c r="B6" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917622</v>
       </c>
       <c r="B7" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135888945</v>
       </c>
       <c r="B9" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135889310</v>
       </c>
       <c r="B10" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135890261</v>
       </c>
       <c r="B11" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>135890410</v>
       </c>
       <c r="B12" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135890469</v>
       </c>
       <c r="B13" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135917603</v>
       </c>
       <c r="B14" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135917607</v>
       </c>
       <c r="B15" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135945068</v>
       </c>
       <c r="B16" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135945090</v>
       </c>
       <c r="B17" t="n">
-        <v>92079</v>
+        <v>92080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>135890793</v>
       </c>
       <c r="B23" t="n">
-        <v>92407</v>
+        <v>92408</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>135889516</v>
       </c>
       <c r="B31" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>135944174</v>
       </c>
       <c r="B32" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>135917605</v>
       </c>
       <c r="B33" t="n">
-        <v>92290</v>
+        <v>92291</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>135944194</v>
       </c>
       <c r="B34" t="n">
-        <v>92290</v>
+        <v>92291</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>135887935</v>
       </c>
       <c r="B35" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>135917600</v>
       </c>
       <c r="B36" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135917609</v>
       </c>
       <c r="B37" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>135917632</v>
       </c>
       <c r="B38" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>135944171</v>
       </c>
       <c r="B39" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135944197</v>
       </c>
       <c r="B40" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>135945066</v>
       </c>
       <c r="B41" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>135945067</v>
       </c>
       <c r="B42" t="n">
-        <v>89295</v>
+        <v>89296</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135887747</v>
       </c>
       <c r="B43" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>135890276</v>
       </c>
       <c r="B44" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135944200</v>
       </c>
       <c r="B45" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>476761</v>
       </c>
       <c r="R98" t="n">
-        <v>7044604</v>
+        <v>7044603</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -14493,7 +14493,7 @@
         <v>135888848</v>
       </c>
       <c r="B127" t="n">
-        <v>99296</v>
+        <v>99297</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>135888822</v>
       </c>
       <c r="B128" t="n">
-        <v>99318</v>
+        <v>99319</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>135944179</v>
       </c>
       <c r="B129" t="n">
-        <v>108319</v>
+        <v>108320</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>135888619</v>
       </c>
       <c r="B130" t="n">
-        <v>99198</v>
+        <v>99199</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>476761</v>
       </c>
       <c r="R130" t="n">
-        <v>7044604</v>
+        <v>7044603</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -14936,7 +14936,7 @@
         <v>135889613</v>
       </c>
       <c r="B131" t="n">
-        <v>99198</v>
+        <v>99199</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>135889209</v>
       </c>
       <c r="B132" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>135944165</v>
       </c>
       <c r="B133" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>135889164</v>
       </c>
       <c r="B134" t="n">
-        <v>106420</v>
+        <v>106421</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>135944158</v>
       </c>
       <c r="B135" t="n">
-        <v>106420</v>
+        <v>106421</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>135944178</v>
       </c>
       <c r="B136" t="n">
-        <v>106420</v>
+        <v>106421</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>135944184</v>
       </c>
       <c r="B137" t="n">
-        <v>106420</v>
+        <v>106421</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>135888627</v>
       </c>
       <c r="B141" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>476761</v>
       </c>
       <c r="R141" t="n">
-        <v>7044604</v>
+        <v>7044603</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16143,7 +16143,7 @@
         <v>135889141</v>
       </c>
       <c r="B142" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>135889396</v>
       </c>
       <c r="B143" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>135890358</v>
       </c>
       <c r="B144" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>135917602</v>
       </c>
       <c r="B145" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>135944160</v>
       </c>
       <c r="B146" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>135944191</v>
       </c>
       <c r="B147" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>135944195</v>
       </c>
       <c r="B148" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>135888967</v>
       </c>
       <c r="B149" t="n">
-        <v>99571</v>
+        <v>99572</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>135889868</v>
       </c>
       <c r="B150" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>135944198</v>
       </c>
       <c r="B151" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>135889874</v>
       </c>
       <c r="B152" t="n">
-        <v>98345</v>
+        <v>98346</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135944188</v>
       </c>
       <c r="B153" t="n">
-        <v>101394</v>
+        <v>101395</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 31237-2026 artfynd.xlsx
+++ b/artfynd/A 31237-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890448</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135944192</v>
       </c>
       <c r="B3" t="n">
-        <v>89432</v>
+        <v>89433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135890254</v>
       </c>
       <c r="B4" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917629</v>
       </c>
       <c r="B5" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135888100</v>
       </c>
       <c r="B6" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917622</v>
       </c>
       <c r="B7" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135888945</v>
       </c>
       <c r="B9" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135889310</v>
       </c>
       <c r="B10" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135890261</v>
       </c>
       <c r="B11" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>135890410</v>
       </c>
       <c r="B12" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135890469</v>
       </c>
       <c r="B13" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135917603</v>
       </c>
       <c r="B14" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135917607</v>
       </c>
       <c r="B15" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135945068</v>
       </c>
       <c r="B16" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135945090</v>
       </c>
       <c r="B17" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>135890793</v>
       </c>
       <c r="B23" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135917639</v>
       </c>
       <c r="B24" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>135944181</v>
       </c>
       <c r="B25" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>135945080</v>
       </c>
       <c r="B26" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>135945081</v>
       </c>
       <c r="B27" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>135945082</v>
       </c>
       <c r="B28" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>135945083</v>
       </c>
       <c r="B29" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>135945084</v>
       </c>
       <c r="B30" t="n">
-        <v>80560</v>
+        <v>80561</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>135889516</v>
       </c>
       <c r="B31" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>135944174</v>
       </c>
       <c r="B32" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>135917605</v>
       </c>
       <c r="B33" t="n">
-        <v>92291</v>
+        <v>92292</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>135944194</v>
       </c>
       <c r="B34" t="n">
-        <v>92291</v>
+        <v>92292</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>135887935</v>
       </c>
       <c r="B35" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>135917600</v>
       </c>
       <c r="B36" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135917609</v>
       </c>
       <c r="B37" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>135917632</v>
       </c>
       <c r="B38" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>135944171</v>
       </c>
       <c r="B39" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135944197</v>
       </c>
       <c r="B40" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>135945066</v>
       </c>
       <c r="B41" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>135945067</v>
       </c>
       <c r="B42" t="n">
-        <v>89296</v>
+        <v>89297</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135887747</v>
       </c>
       <c r="B43" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>135890276</v>
       </c>
       <c r="B44" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135944200</v>
       </c>
       <c r="B45" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>135887305</v>
       </c>
       <c r="B48" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>135888884</v>
       </c>
       <c r="B49" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>135889085</v>
       </c>
       <c r="B50" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>135889333</v>
       </c>
       <c r="B51" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135917634</v>
       </c>
       <c r="B52" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135917649</v>
       </c>
       <c r="B53" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>135917650</v>
       </c>
       <c r="B54" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>135917651</v>
       </c>
       <c r="B55" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>135917653</v>
       </c>
       <c r="B56" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>135917655</v>
       </c>
       <c r="B57" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>135917663</v>
       </c>
       <c r="B58" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>135917664</v>
       </c>
       <c r="B59" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>135917666</v>
       </c>
       <c r="B60" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>135944159</v>
       </c>
       <c r="B61" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>135944161</v>
       </c>
       <c r="B62" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>135944164</v>
       </c>
       <c r="B63" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>135944167</v>
       </c>
       <c r="B64" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>135944170</v>
       </c>
       <c r="B65" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>135944172</v>
       </c>
       <c r="B66" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>135944187</v>
       </c>
       <c r="B67" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>135944189</v>
       </c>
       <c r="B68" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>135944190</v>
       </c>
       <c r="B69" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>135944196</v>
       </c>
       <c r="B70" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>135944199</v>
       </c>
       <c r="B71" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>135944202</v>
       </c>
       <c r="B72" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>135945091</v>
       </c>
       <c r="B73" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135945092</v>
       </c>
       <c r="B74" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>135888499</v>
       </c>
       <c r="B75" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>135888120</v>
       </c>
       <c r="B76" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>135917620</v>
       </c>
       <c r="B77" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>135917631</v>
       </c>
       <c r="B78" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>135945085</v>
       </c>
       <c r="B79" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>135945086</v>
       </c>
       <c r="B80" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>135945087</v>
       </c>
       <c r="B81" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>135945088</v>
       </c>
       <c r="B82" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>135945089</v>
       </c>
       <c r="B83" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>135945094</v>
       </c>
       <c r="B84" t="n">
-        <v>79700</v>
+        <v>79701</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>135888337</v>
       </c>
       <c r="B86" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>135888567</v>
       </c>
       <c r="B87" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>135889256</v>
       </c>
       <c r="B88" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>135890496</v>
       </c>
       <c r="B89" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>135917621</v>
       </c>
       <c r="B90" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>135888326</v>
       </c>
       <c r="B91" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>135945093</v>
       </c>
       <c r="B92" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>135888134</v>
       </c>
       <c r="B93" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>135944177</v>
       </c>
       <c r="B94" t="n">
-        <v>80571</v>
+        <v>80572</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>135888984</v>
       </c>
       <c r="B95" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>135944169</v>
       </c>
       <c r="B96" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>135888059</v>
       </c>
       <c r="B97" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>135888595</v>
       </c>
       <c r="B98" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>476761</v>
       </c>
       <c r="R98" t="n">
-        <v>7044603</v>
+        <v>7044604</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11143,7 +11143,7 @@
         <v>135888744</v>
       </c>
       <c r="B99" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>135888896</v>
       </c>
       <c r="B100" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>135889188</v>
       </c>
       <c r="B101" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>135889243</v>
       </c>
       <c r="B102" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>135889343</v>
       </c>
       <c r="B103" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>135890314</v>
       </c>
       <c r="B104" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>135917612</v>
       </c>
       <c r="B105" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>135917618</v>
       </c>
       <c r="B106" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>135917637</v>
       </c>
       <c r="B107" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>135917656</v>
       </c>
       <c r="B108" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>135917657</v>
       </c>
       <c r="B109" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>135917659</v>
       </c>
       <c r="B110" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>135917661</v>
       </c>
       <c r="B111" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>135917668</v>
       </c>
       <c r="B112" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>135917669</v>
       </c>
       <c r="B113" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>135944193</v>
       </c>
       <c r="B114" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>135945069</v>
       </c>
       <c r="B115" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>135945070</v>
       </c>
       <c r="B116" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>135945071</v>
       </c>
       <c r="B117" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>135945072</v>
       </c>
       <c r="B118" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>135945073</v>
       </c>
       <c r="B119" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>135945074</v>
       </c>
       <c r="B120" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>135945075</v>
       </c>
       <c r="B121" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>135945076</v>
       </c>
       <c r="B122" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>135917641</v>
       </c>
       <c r="B123" t="n">
-        <v>57160</v>
+        <v>57161</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>135888587</v>
       </c>
       <c r="B124" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>135889674</v>
       </c>
       <c r="B125" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>135945077</v>
       </c>
       <c r="B126" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>135888848</v>
       </c>
       <c r="B127" t="n">
-        <v>99297</v>
+        <v>99298</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>135888822</v>
       </c>
       <c r="B128" t="n">
-        <v>99319</v>
+        <v>99320</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>135944179</v>
       </c>
       <c r="B129" t="n">
-        <v>108320</v>
+        <v>108321</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>135888619</v>
       </c>
       <c r="B130" t="n">
-        <v>99199</v>
+        <v>99200</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>476761</v>
       </c>
       <c r="R130" t="n">
-        <v>7044603</v>
+        <v>7044604</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -14936,7 +14936,7 @@
         <v>135889613</v>
       </c>
       <c r="B131" t="n">
-        <v>99199</v>
+        <v>99200</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>135889209</v>
       </c>
       <c r="B132" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>135944165</v>
       </c>
       <c r="B133" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>135889164</v>
       </c>
       <c r="B134" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>135944158</v>
       </c>
       <c r="B135" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>135944178</v>
       </c>
       <c r="B136" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>135944184</v>
       </c>
       <c r="B137" t="n">
-        <v>106421</v>
+        <v>106422</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>135888627</v>
       </c>
       <c r="B141" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>476761</v>
       </c>
       <c r="R141" t="n">
-        <v>7044603</v>
+        <v>7044604</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16143,7 +16143,7 @@
         <v>135889141</v>
       </c>
       <c r="B142" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>135889396</v>
       </c>
       <c r="B143" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>135890358</v>
       </c>
       <c r="B144" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>135917602</v>
       </c>
       <c r="B145" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>135944160</v>
       </c>
       <c r="B146" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>135944191</v>
       </c>
       <c r="B147" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>135944195</v>
       </c>
       <c r="B148" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>135888967</v>
       </c>
       <c r="B149" t="n">
-        <v>99572</v>
+        <v>99573</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>135889868</v>
       </c>
       <c r="B150" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>135944198</v>
       </c>
       <c r="B151" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>135889874</v>
       </c>
       <c r="B152" t="n">
-        <v>98346</v>
+        <v>98347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135944188</v>
       </c>
       <c r="B153" t="n">
-        <v>101395</v>
+        <v>101396</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 31237-2026 artfynd.xlsx
+++ b/artfynd/A 31237-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890448</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135944192</v>
       </c>
       <c r="B3" t="n">
-        <v>89433</v>
+        <v>89439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135890254</v>
       </c>
       <c r="B4" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917629</v>
       </c>
       <c r="B5" t="n">
-        <v>92640</v>
+        <v>92646</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135888100</v>
       </c>
       <c r="B6" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917622</v>
       </c>
       <c r="B7" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135888945</v>
       </c>
       <c r="B9" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135889310</v>
       </c>
       <c r="B10" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135890261</v>
       </c>
       <c r="B11" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>135890410</v>
       </c>
       <c r="B12" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135890469</v>
       </c>
       <c r="B13" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135917603</v>
       </c>
       <c r="B14" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135917607</v>
       </c>
       <c r="B15" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135945068</v>
       </c>
       <c r="B16" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135945090</v>
       </c>
       <c r="B17" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>135890793</v>
       </c>
       <c r="B23" t="n">
-        <v>92409</v>
+        <v>92415</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135917639</v>
       </c>
       <c r="B24" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>135944181</v>
       </c>
       <c r="B25" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>135945080</v>
       </c>
       <c r="B26" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>135945081</v>
       </c>
       <c r="B27" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>135945082</v>
       </c>
       <c r="B28" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>135945083</v>
       </c>
       <c r="B29" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>135945084</v>
       </c>
       <c r="B30" t="n">
-        <v>80561</v>
+        <v>80565</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>135889516</v>
       </c>
       <c r="B31" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>135944174</v>
       </c>
       <c r="B32" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>135917605</v>
       </c>
       <c r="B33" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>135944194</v>
       </c>
       <c r="B34" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>135887935</v>
       </c>
       <c r="B35" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>135917600</v>
       </c>
       <c r="B36" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135917609</v>
       </c>
       <c r="B37" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>135917632</v>
       </c>
       <c r="B38" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>135944171</v>
       </c>
       <c r="B39" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135944197</v>
       </c>
       <c r="B40" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>135945066</v>
       </c>
       <c r="B41" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>135945067</v>
       </c>
       <c r="B42" t="n">
-        <v>89297</v>
+        <v>89303</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135887747</v>
       </c>
       <c r="B43" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>135890276</v>
       </c>
       <c r="B44" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135944200</v>
       </c>
       <c r="B45" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>135887305</v>
       </c>
       <c r="B48" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>135888884</v>
       </c>
       <c r="B49" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>135889085</v>
       </c>
       <c r="B50" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>135889333</v>
       </c>
       <c r="B51" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135917634</v>
       </c>
       <c r="B52" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135917649</v>
       </c>
       <c r="B53" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>135917650</v>
       </c>
       <c r="B54" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>135917651</v>
       </c>
       <c r="B55" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>135917653</v>
       </c>
       <c r="B56" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>135917655</v>
       </c>
       <c r="B57" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>135917663</v>
       </c>
       <c r="B58" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>135917664</v>
       </c>
       <c r="B59" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>135917666</v>
       </c>
       <c r="B60" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>135944159</v>
       </c>
       <c r="B61" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>135944161</v>
       </c>
       <c r="B62" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>135944164</v>
       </c>
       <c r="B63" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>135944167</v>
       </c>
       <c r="B64" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>135944170</v>
       </c>
       <c r="B65" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>135944172</v>
       </c>
       <c r="B66" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>135944187</v>
       </c>
       <c r="B67" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>135944189</v>
       </c>
       <c r="B68" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>135944190</v>
       </c>
       <c r="B69" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>135944196</v>
       </c>
       <c r="B70" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>135944199</v>
       </c>
       <c r="B71" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>135944202</v>
       </c>
       <c r="B72" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>135945091</v>
       </c>
       <c r="B73" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135945092</v>
       </c>
       <c r="B74" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>135888499</v>
       </c>
       <c r="B75" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>135888120</v>
       </c>
       <c r="B76" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>135917620</v>
       </c>
       <c r="B77" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>135917631</v>
       </c>
       <c r="B78" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>135945085</v>
       </c>
       <c r="B79" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>135945086</v>
       </c>
       <c r="B80" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>135945087</v>
       </c>
       <c r="B81" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>135945088</v>
       </c>
       <c r="B82" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>135945089</v>
       </c>
       <c r="B83" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>135945094</v>
       </c>
       <c r="B84" t="n">
-        <v>79701</v>
+        <v>79705</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>135888337</v>
       </c>
       <c r="B86" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>135888567</v>
       </c>
       <c r="B87" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>135889256</v>
       </c>
       <c r="B88" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>135890496</v>
       </c>
       <c r="B89" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>135917621</v>
       </c>
       <c r="B90" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>135888326</v>
       </c>
       <c r="B91" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>135945093</v>
       </c>
       <c r="B92" t="n">
-        <v>80571</v>
+        <v>80575</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>135888134</v>
       </c>
       <c r="B93" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>135944177</v>
       </c>
       <c r="B94" t="n">
-        <v>80572</v>
+        <v>80576</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>135888984</v>
       </c>
       <c r="B95" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>135944169</v>
       </c>
       <c r="B96" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>135888059</v>
       </c>
       <c r="B97" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>135888595</v>
       </c>
       <c r="B98" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>476761</v>
       </c>
       <c r="R98" t="n">
-        <v>7044604</v>
+        <v>7044603</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11143,7 +11143,7 @@
         <v>135888744</v>
       </c>
       <c r="B99" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>135888896</v>
       </c>
       <c r="B100" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>135889188</v>
       </c>
       <c r="B101" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>135889243</v>
       </c>
       <c r="B102" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>135889343</v>
       </c>
       <c r="B103" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>135890314</v>
       </c>
       <c r="B104" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>135917612</v>
       </c>
       <c r="B105" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>135917618</v>
       </c>
       <c r="B106" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>135917637</v>
       </c>
       <c r="B107" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>135917656</v>
       </c>
       <c r="B108" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>135917657</v>
       </c>
       <c r="B109" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>135917659</v>
       </c>
       <c r="B110" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>135917661</v>
       </c>
       <c r="B111" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>135917668</v>
       </c>
       <c r="B112" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>135917669</v>
       </c>
       <c r="B113" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>135944193</v>
       </c>
       <c r="B114" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>135945069</v>
       </c>
       <c r="B115" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>135945070</v>
       </c>
       <c r="B116" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>135945071</v>
       </c>
       <c r="B117" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>135945072</v>
       </c>
       <c r="B118" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>135945073</v>
       </c>
       <c r="B119" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>135945074</v>
       </c>
       <c r="B120" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>135945075</v>
       </c>
       <c r="B121" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>135945076</v>
       </c>
       <c r="B122" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>135917641</v>
       </c>
       <c r="B123" t="n">
-        <v>57161</v>
+        <v>57165</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>135888587</v>
       </c>
       <c r="B124" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>135889674</v>
       </c>
       <c r="B125" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>135945077</v>
       </c>
       <c r="B126" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>135888848</v>
       </c>
       <c r="B127" t="n">
-        <v>99298</v>
+        <v>99304</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>135888822</v>
       </c>
       <c r="B128" t="n">
-        <v>99320</v>
+        <v>99326</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>135944179</v>
       </c>
       <c r="B129" t="n">
-        <v>108321</v>
+        <v>108327</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>135888619</v>
       </c>
       <c r="B130" t="n">
-        <v>99200</v>
+        <v>99206</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>476761</v>
       </c>
       <c r="R130" t="n">
-        <v>7044604</v>
+        <v>7044603</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -14936,7 +14936,7 @@
         <v>135889613</v>
       </c>
       <c r="B131" t="n">
-        <v>99200</v>
+        <v>99206</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>135889209</v>
       </c>
       <c r="B132" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>135944165</v>
       </c>
       <c r="B133" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>135889164</v>
       </c>
       <c r="B134" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>135944158</v>
       </c>
       <c r="B135" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>135944178</v>
       </c>
       <c r="B136" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>135944184</v>
       </c>
       <c r="B137" t="n">
-        <v>106422</v>
+        <v>106428</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>135888627</v>
       </c>
       <c r="B141" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>476761</v>
       </c>
       <c r="R141" t="n">
-        <v>7044604</v>
+        <v>7044603</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16143,7 +16143,7 @@
         <v>135889141</v>
       </c>
       <c r="B142" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>135889396</v>
       </c>
       <c r="B143" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>135890358</v>
       </c>
       <c r="B144" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>135917602</v>
       </c>
       <c r="B145" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>135944160</v>
       </c>
       <c r="B146" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>135944191</v>
       </c>
       <c r="B147" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>135944195</v>
       </c>
       <c r="B148" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>135888967</v>
       </c>
       <c r="B149" t="n">
-        <v>99573</v>
+        <v>99579</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>135889868</v>
       </c>
       <c r="B150" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>135944198</v>
       </c>
       <c r="B151" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>135889874</v>
       </c>
       <c r="B152" t="n">
-        <v>98347</v>
+        <v>98353</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135944188</v>
       </c>
       <c r="B153" t="n">
-        <v>101396</v>
+        <v>101402</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 31237-2026 artfynd.xlsx
+++ b/artfynd/A 31237-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890448</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135944192</v>
       </c>
       <c r="B3" t="n">
-        <v>89439</v>
+        <v>89440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135890254</v>
       </c>
       <c r="B4" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917629</v>
       </c>
       <c r="B5" t="n">
-        <v>92646</v>
+        <v>92647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135888100</v>
       </c>
       <c r="B6" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917622</v>
       </c>
       <c r="B7" t="n">
-        <v>92069</v>
+        <v>92070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135888945</v>
       </c>
       <c r="B9" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135889310</v>
       </c>
       <c r="B10" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135890261</v>
       </c>
       <c r="B11" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>135890410</v>
       </c>
       <c r="B12" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135890469</v>
       </c>
       <c r="B13" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135917603</v>
       </c>
       <c r="B14" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135917607</v>
       </c>
       <c r="B15" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135945068</v>
       </c>
       <c r="B16" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135945090</v>
       </c>
       <c r="B17" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>135890793</v>
       </c>
       <c r="B23" t="n">
-        <v>92415</v>
+        <v>92416</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135917639</v>
       </c>
       <c r="B24" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>135944181</v>
       </c>
       <c r="B25" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>135945080</v>
       </c>
       <c r="B26" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>135945081</v>
       </c>
       <c r="B27" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>135945082</v>
       </c>
       <c r="B28" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>135945083</v>
       </c>
       <c r="B29" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>135945084</v>
       </c>
       <c r="B30" t="n">
-        <v>80565</v>
+        <v>80566</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>135889516</v>
       </c>
       <c r="B31" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>135944174</v>
       </c>
       <c r="B32" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>135917605</v>
       </c>
       <c r="B33" t="n">
-        <v>92298</v>
+        <v>92299</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>135944194</v>
       </c>
       <c r="B34" t="n">
-        <v>92298</v>
+        <v>92299</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>135887935</v>
       </c>
       <c r="B35" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>135917600</v>
       </c>
       <c r="B36" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135917609</v>
       </c>
       <c r="B37" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>135917632</v>
       </c>
       <c r="B38" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>135944171</v>
       </c>
       <c r="B39" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135944197</v>
       </c>
       <c r="B40" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>135945066</v>
       </c>
       <c r="B41" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>135945067</v>
       </c>
       <c r="B42" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135887747</v>
       </c>
       <c r="B43" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>135890276</v>
       </c>
       <c r="B44" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135944200</v>
       </c>
       <c r="B45" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>135887305</v>
       </c>
       <c r="B48" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>135888884</v>
       </c>
       <c r="B49" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>135889085</v>
       </c>
       <c r="B50" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>135889333</v>
       </c>
       <c r="B51" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135917634</v>
       </c>
       <c r="B52" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135917649</v>
       </c>
       <c r="B53" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>135917650</v>
       </c>
       <c r="B54" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>135917651</v>
       </c>
       <c r="B55" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>135917653</v>
       </c>
       <c r="B56" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>135917655</v>
       </c>
       <c r="B57" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>135917663</v>
       </c>
       <c r="B58" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>135917664</v>
       </c>
       <c r="B59" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>135917666</v>
       </c>
       <c r="B60" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>135944159</v>
       </c>
       <c r="B61" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>135944161</v>
       </c>
       <c r="B62" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>135944164</v>
       </c>
       <c r="B63" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>135944167</v>
       </c>
       <c r="B64" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>135944170</v>
       </c>
       <c r="B65" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>135944172</v>
       </c>
       <c r="B66" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>135944187</v>
       </c>
       <c r="B67" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>135944189</v>
       </c>
       <c r="B68" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>135944190</v>
       </c>
       <c r="B69" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>135944196</v>
       </c>
       <c r="B70" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>135944199</v>
       </c>
       <c r="B71" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>135944202</v>
       </c>
       <c r="B72" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>135945091</v>
       </c>
       <c r="B73" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135945092</v>
       </c>
       <c r="B74" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>135888499</v>
       </c>
       <c r="B75" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>135888120</v>
       </c>
       <c r="B76" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>135917620</v>
       </c>
       <c r="B77" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>135917631</v>
       </c>
       <c r="B78" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>135945085</v>
       </c>
       <c r="B79" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>135945086</v>
       </c>
       <c r="B80" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>135945087</v>
       </c>
       <c r="B81" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>135945088</v>
       </c>
       <c r="B82" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>135945089</v>
       </c>
       <c r="B83" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>135945094</v>
       </c>
       <c r="B84" t="n">
-        <v>79705</v>
+        <v>79706</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>135888337</v>
       </c>
       <c r="B86" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>135888567</v>
       </c>
       <c r="B87" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>135889256</v>
       </c>
       <c r="B88" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>135890496</v>
       </c>
       <c r="B89" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>135917621</v>
       </c>
       <c r="B90" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>135888326</v>
       </c>
       <c r="B91" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>135945093</v>
       </c>
       <c r="B92" t="n">
-        <v>80575</v>
+        <v>80576</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>135888134</v>
       </c>
       <c r="B93" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>135944177</v>
       </c>
       <c r="B94" t="n">
-        <v>80576</v>
+        <v>80577</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>135888984</v>
       </c>
       <c r="B95" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>135944169</v>
       </c>
       <c r="B96" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>135888059</v>
       </c>
       <c r="B97" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>135888595</v>
       </c>
       <c r="B98" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>476761</v>
       </c>
       <c r="R98" t="n">
-        <v>7044603</v>
+        <v>7044604</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11143,7 +11143,7 @@
         <v>135888744</v>
       </c>
       <c r="B99" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>135888896</v>
       </c>
       <c r="B100" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>135889188</v>
       </c>
       <c r="B101" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>135889243</v>
       </c>
       <c r="B102" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>135889343</v>
       </c>
       <c r="B103" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>135890314</v>
       </c>
       <c r="B104" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>135917612</v>
       </c>
       <c r="B105" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>135917618</v>
       </c>
       <c r="B106" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>135917637</v>
       </c>
       <c r="B107" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>135917656</v>
       </c>
       <c r="B108" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>135917657</v>
       </c>
       <c r="B109" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>135917659</v>
       </c>
       <c r="B110" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>135917661</v>
       </c>
       <c r="B111" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>135917668</v>
       </c>
       <c r="B112" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>135917669</v>
       </c>
       <c r="B113" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>135944193</v>
       </c>
       <c r="B114" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>135945069</v>
       </c>
       <c r="B115" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>135945070</v>
       </c>
       <c r="B116" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>135945071</v>
       </c>
       <c r="B117" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>135945072</v>
       </c>
       <c r="B118" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>135945073</v>
       </c>
       <c r="B119" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>135945074</v>
       </c>
       <c r="B120" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>135945075</v>
       </c>
       <c r="B121" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>135945076</v>
       </c>
       <c r="B122" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>135917641</v>
       </c>
       <c r="B123" t="n">
-        <v>57165</v>
+        <v>57166</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>135888587</v>
       </c>
       <c r="B124" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>135889674</v>
       </c>
       <c r="B125" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>135945077</v>
       </c>
       <c r="B126" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>135888848</v>
       </c>
       <c r="B127" t="n">
-        <v>99304</v>
+        <v>99305</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>135888822</v>
       </c>
       <c r="B128" t="n">
-        <v>99326</v>
+        <v>99327</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>135944179</v>
       </c>
       <c r="B129" t="n">
-        <v>108327</v>
+        <v>108328</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>135888619</v>
       </c>
       <c r="B130" t="n">
-        <v>99206</v>
+        <v>99207</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>476761</v>
       </c>
       <c r="R130" t="n">
-        <v>7044603</v>
+        <v>7044604</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -14936,7 +14936,7 @@
         <v>135889613</v>
       </c>
       <c r="B131" t="n">
-        <v>99206</v>
+        <v>99207</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>135889209</v>
       </c>
       <c r="B132" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>135944165</v>
       </c>
       <c r="B133" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>135889164</v>
       </c>
       <c r="B134" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>135944158</v>
       </c>
       <c r="B135" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>135944178</v>
       </c>
       <c r="B136" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>135944184</v>
       </c>
       <c r="B137" t="n">
-        <v>106428</v>
+        <v>106429</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>135888627</v>
       </c>
       <c r="B141" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>476761</v>
       </c>
       <c r="R141" t="n">
-        <v>7044603</v>
+        <v>7044604</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16143,7 +16143,7 @@
         <v>135889141</v>
       </c>
       <c r="B142" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>135889396</v>
       </c>
       <c r="B143" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>135890358</v>
       </c>
       <c r="B144" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>135917602</v>
       </c>
       <c r="B145" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>135944160</v>
       </c>
       <c r="B146" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>135944191</v>
       </c>
       <c r="B147" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>135944195</v>
       </c>
       <c r="B148" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>135888967</v>
       </c>
       <c r="B149" t="n">
-        <v>99579</v>
+        <v>99580</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>135889868</v>
       </c>
       <c r="B150" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>135944198</v>
       </c>
       <c r="B151" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>135889874</v>
       </c>
       <c r="B152" t="n">
-        <v>98353</v>
+        <v>98354</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135944188</v>
       </c>
       <c r="B153" t="n">
-        <v>101402</v>
+        <v>101403</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 31237-2026 artfynd.xlsx
+++ b/artfynd/A 31237-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890448</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135944192</v>
       </c>
       <c r="B3" t="n">
-        <v>89440</v>
+        <v>89446</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135890254</v>
       </c>
       <c r="B4" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917629</v>
       </c>
       <c r="B5" t="n">
-        <v>92647</v>
+        <v>92653</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135888100</v>
       </c>
       <c r="B6" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917622</v>
       </c>
       <c r="B7" t="n">
-        <v>92070</v>
+        <v>92076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135888945</v>
       </c>
       <c r="B9" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135889310</v>
       </c>
       <c r="B10" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135890261</v>
       </c>
       <c r="B11" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>135890410</v>
       </c>
       <c r="B12" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135890469</v>
       </c>
       <c r="B13" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135917603</v>
       </c>
       <c r="B14" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135917607</v>
       </c>
       <c r="B15" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135945068</v>
       </c>
       <c r="B16" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135945090</v>
       </c>
       <c r="B17" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>135890793</v>
       </c>
       <c r="B23" t="n">
-        <v>92416</v>
+        <v>92422</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135917639</v>
       </c>
       <c r="B24" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>135944181</v>
       </c>
       <c r="B25" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>135945080</v>
       </c>
       <c r="B26" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>135945081</v>
       </c>
       <c r="B27" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>135945082</v>
       </c>
       <c r="B28" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>135945083</v>
       </c>
       <c r="B29" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>135945084</v>
       </c>
       <c r="B30" t="n">
-        <v>80566</v>
+        <v>80570</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>135889516</v>
       </c>
       <c r="B31" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>135944174</v>
       </c>
       <c r="B32" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>135917605</v>
       </c>
       <c r="B33" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>135944194</v>
       </c>
       <c r="B34" t="n">
-        <v>92299</v>
+        <v>92305</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>135887935</v>
       </c>
       <c r="B35" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>135917600</v>
       </c>
       <c r="B36" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135917609</v>
       </c>
       <c r="B37" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>135917632</v>
       </c>
       <c r="B38" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>135944171</v>
       </c>
       <c r="B39" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135944197</v>
       </c>
       <c r="B40" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>135945066</v>
       </c>
       <c r="B41" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>135945067</v>
       </c>
       <c r="B42" t="n">
-        <v>89304</v>
+        <v>89310</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135887747</v>
       </c>
       <c r="B43" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>135890276</v>
       </c>
       <c r="B44" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135944200</v>
       </c>
       <c r="B45" t="n">
-        <v>92037</v>
+        <v>92043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>135887305</v>
       </c>
       <c r="B48" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>135888884</v>
       </c>
       <c r="B49" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>135889085</v>
       </c>
       <c r="B50" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>135889333</v>
       </c>
       <c r="B51" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135917634</v>
       </c>
       <c r="B52" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135917649</v>
       </c>
       <c r="B53" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>135917650</v>
       </c>
       <c r="B54" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>135917651</v>
       </c>
       <c r="B55" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>135917653</v>
       </c>
       <c r="B56" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>135917655</v>
       </c>
       <c r="B57" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>135917663</v>
       </c>
       <c r="B58" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>135917664</v>
       </c>
       <c r="B59" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>135917666</v>
       </c>
       <c r="B60" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>135944159</v>
       </c>
       <c r="B61" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>135944161</v>
       </c>
       <c r="B62" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>135944164</v>
       </c>
       <c r="B63" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>135944167</v>
       </c>
       <c r="B64" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>135944170</v>
       </c>
       <c r="B65" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>135944172</v>
       </c>
       <c r="B66" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>135944187</v>
       </c>
       <c r="B67" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>135944189</v>
       </c>
       <c r="B68" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>135944190</v>
       </c>
       <c r="B69" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>135944196</v>
       </c>
       <c r="B70" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>135944199</v>
       </c>
       <c r="B71" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>135944202</v>
       </c>
       <c r="B72" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>135945091</v>
       </c>
       <c r="B73" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135945092</v>
       </c>
       <c r="B74" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>135888499</v>
       </c>
       <c r="B75" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>135888120</v>
       </c>
       <c r="B76" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>135917620</v>
       </c>
       <c r="B77" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>135917631</v>
       </c>
       <c r="B78" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>135945085</v>
       </c>
       <c r="B79" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>135945086</v>
       </c>
       <c r="B80" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>135945087</v>
       </c>
       <c r="B81" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>135945088</v>
       </c>
       <c r="B82" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>135945089</v>
       </c>
       <c r="B83" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>135945094</v>
       </c>
       <c r="B84" t="n">
-        <v>79706</v>
+        <v>79710</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>135888337</v>
       </c>
       <c r="B86" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>135888567</v>
       </c>
       <c r="B87" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>135889256</v>
       </c>
       <c r="B88" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>135890496</v>
       </c>
       <c r="B89" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>135917621</v>
       </c>
       <c r="B90" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>135888326</v>
       </c>
       <c r="B91" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>135945093</v>
       </c>
       <c r="B92" t="n">
-        <v>80576</v>
+        <v>80580</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>135888134</v>
       </c>
       <c r="B93" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>135944177</v>
       </c>
       <c r="B94" t="n">
-        <v>80577</v>
+        <v>80581</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>135888848</v>
       </c>
       <c r="B127" t="n">
-        <v>99305</v>
+        <v>99316</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>135888822</v>
       </c>
       <c r="B128" t="n">
-        <v>99327</v>
+        <v>99338</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>135944179</v>
       </c>
       <c r="B129" t="n">
-        <v>108328</v>
+        <v>108339</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>135888619</v>
       </c>
       <c r="B130" t="n">
-        <v>99207</v>
+        <v>99218</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>135889613</v>
       </c>
       <c r="B131" t="n">
-        <v>99207</v>
+        <v>99218</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>135889209</v>
       </c>
       <c r="B132" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>135944165</v>
       </c>
       <c r="B133" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>135889164</v>
       </c>
       <c r="B134" t="n">
-        <v>106429</v>
+        <v>106440</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>135944158</v>
       </c>
       <c r="B135" t="n">
-        <v>106429</v>
+        <v>106440</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>135944178</v>
       </c>
       <c r="B136" t="n">
-        <v>106429</v>
+        <v>106440</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>135944184</v>
       </c>
       <c r="B137" t="n">
-        <v>106429</v>
+        <v>106440</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>135888627</v>
       </c>
       <c r="B141" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>135889141</v>
       </c>
       <c r="B142" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>135889396</v>
       </c>
       <c r="B143" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>135890358</v>
       </c>
       <c r="B144" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>135917602</v>
       </c>
       <c r="B145" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>135944160</v>
       </c>
       <c r="B146" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>135944191</v>
       </c>
       <c r="B147" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>135944195</v>
       </c>
       <c r="B148" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>135888967</v>
       </c>
       <c r="B149" t="n">
-        <v>99580</v>
+        <v>99591</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>135889868</v>
       </c>
       <c r="B150" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>135944198</v>
       </c>
       <c r="B151" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>135889874</v>
       </c>
       <c r="B152" t="n">
-        <v>98354</v>
+        <v>98365</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135944188</v>
       </c>
       <c r="B153" t="n">
-        <v>101403</v>
+        <v>101414</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 31237-2026 artfynd.xlsx
+++ b/artfynd/A 31237-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890448</v>
       </c>
       <c r="B2" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135944192</v>
       </c>
       <c r="B3" t="n">
-        <v>89446</v>
+        <v>89453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135890254</v>
       </c>
       <c r="B4" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917629</v>
       </c>
       <c r="B5" t="n">
-        <v>92653</v>
+        <v>92660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135888100</v>
       </c>
       <c r="B6" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917622</v>
       </c>
       <c r="B7" t="n">
-        <v>92076</v>
+        <v>92083</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135888945</v>
       </c>
       <c r="B9" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135889310</v>
       </c>
       <c r="B10" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135890261</v>
       </c>
       <c r="B11" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>135890410</v>
       </c>
       <c r="B12" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135890469</v>
       </c>
       <c r="B13" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135917603</v>
       </c>
       <c r="B14" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135917607</v>
       </c>
       <c r="B15" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135945068</v>
       </c>
       <c r="B16" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135945090</v>
       </c>
       <c r="B17" t="n">
-        <v>92094</v>
+        <v>92101</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>135890793</v>
       </c>
       <c r="B23" t="n">
-        <v>92422</v>
+        <v>92429</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135917639</v>
       </c>
       <c r="B24" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>135944181</v>
       </c>
       <c r="B25" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>135945080</v>
       </c>
       <c r="B26" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>135945081</v>
       </c>
       <c r="B27" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>135945082</v>
       </c>
       <c r="B28" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>135945083</v>
       </c>
       <c r="B29" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>135945084</v>
       </c>
       <c r="B30" t="n">
-        <v>80570</v>
+        <v>80576</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>135889516</v>
       </c>
       <c r="B31" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>135944174</v>
       </c>
       <c r="B32" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>135917605</v>
       </c>
       <c r="B33" t="n">
-        <v>92305</v>
+        <v>92312</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>135944194</v>
       </c>
       <c r="B34" t="n">
-        <v>92305</v>
+        <v>92312</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>135887935</v>
       </c>
       <c r="B35" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>135917600</v>
       </c>
       <c r="B36" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135917609</v>
       </c>
       <c r="B37" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>135917632</v>
       </c>
       <c r="B38" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>135944171</v>
       </c>
       <c r="B39" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135944197</v>
       </c>
       <c r="B40" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>135945066</v>
       </c>
       <c r="B41" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>135945067</v>
       </c>
       <c r="B42" t="n">
-        <v>89310</v>
+        <v>89317</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135887747</v>
       </c>
       <c r="B43" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>135890276</v>
       </c>
       <c r="B44" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135944200</v>
       </c>
       <c r="B45" t="n">
-        <v>92043</v>
+        <v>92050</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>135887305</v>
       </c>
       <c r="B48" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>135888884</v>
       </c>
       <c r="B49" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>135889085</v>
       </c>
       <c r="B50" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>135889333</v>
       </c>
       <c r="B51" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135917634</v>
       </c>
       <c r="B52" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135917649</v>
       </c>
       <c r="B53" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>135917650</v>
       </c>
       <c r="B54" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>135917651</v>
       </c>
       <c r="B55" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>135917653</v>
       </c>
       <c r="B56" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>135917655</v>
       </c>
       <c r="B57" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>135917663</v>
       </c>
       <c r="B58" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>135917664</v>
       </c>
       <c r="B59" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>135917666</v>
       </c>
       <c r="B60" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>135944159</v>
       </c>
       <c r="B61" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>135944161</v>
       </c>
       <c r="B62" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>135944164</v>
       </c>
       <c r="B63" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>135944167</v>
       </c>
       <c r="B64" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>135944170</v>
       </c>
       <c r="B65" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>135944172</v>
       </c>
       <c r="B66" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>135944187</v>
       </c>
       <c r="B67" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>135944189</v>
       </c>
       <c r="B68" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>135944190</v>
       </c>
       <c r="B69" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>135944196</v>
       </c>
       <c r="B70" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>135944199</v>
       </c>
       <c r="B71" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>135944202</v>
       </c>
       <c r="B72" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>135945091</v>
       </c>
       <c r="B73" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135945092</v>
       </c>
       <c r="B74" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>135888499</v>
       </c>
       <c r="B75" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>135888120</v>
       </c>
       <c r="B76" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>135917620</v>
       </c>
       <c r="B77" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>135917631</v>
       </c>
       <c r="B78" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>135945085</v>
       </c>
       <c r="B79" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>135945086</v>
       </c>
       <c r="B80" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>135945087</v>
       </c>
       <c r="B81" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>135945088</v>
       </c>
       <c r="B82" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>135945089</v>
       </c>
       <c r="B83" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>135945094</v>
       </c>
       <c r="B84" t="n">
-        <v>79710</v>
+        <v>79716</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>135888337</v>
       </c>
       <c r="B86" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>135888567</v>
       </c>
       <c r="B87" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>135889256</v>
       </c>
       <c r="B88" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>135890496</v>
       </c>
       <c r="B89" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>135917621</v>
       </c>
       <c r="B90" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>135888326</v>
       </c>
       <c r="B91" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>135945093</v>
       </c>
       <c r="B92" t="n">
-        <v>80580</v>
+        <v>80586</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>135888134</v>
       </c>
       <c r="B93" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>135944177</v>
       </c>
       <c r="B94" t="n">
-        <v>80581</v>
+        <v>80587</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>135888984</v>
       </c>
       <c r="B95" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>135944169</v>
       </c>
       <c r="B96" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>135888059</v>
       </c>
       <c r="B97" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>135888595</v>
       </c>
       <c r="B98" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>135888744</v>
       </c>
       <c r="B99" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>135888896</v>
       </c>
       <c r="B100" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>135889188</v>
       </c>
       <c r="B101" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>135889243</v>
       </c>
       <c r="B102" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>135889343</v>
       </c>
       <c r="B103" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>135890314</v>
       </c>
       <c r="B104" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>135917612</v>
       </c>
       <c r="B105" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>135917618</v>
       </c>
       <c r="B106" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>135917637</v>
       </c>
       <c r="B107" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>135917656</v>
       </c>
       <c r="B108" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>135917657</v>
       </c>
       <c r="B109" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>135917659</v>
       </c>
       <c r="B110" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>135917661</v>
       </c>
       <c r="B111" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>135917668</v>
       </c>
       <c r="B112" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>135917669</v>
       </c>
       <c r="B113" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>135944193</v>
       </c>
       <c r="B114" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>135945069</v>
       </c>
       <c r="B115" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>135945070</v>
       </c>
       <c r="B116" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>135945071</v>
       </c>
       <c r="B117" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>135945072</v>
       </c>
       <c r="B118" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>135945073</v>
       </c>
       <c r="B119" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>135945074</v>
       </c>
       <c r="B120" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>135945075</v>
       </c>
       <c r="B121" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>135945076</v>
       </c>
       <c r="B122" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>135917641</v>
       </c>
       <c r="B123" t="n">
-        <v>57166</v>
+        <v>57171</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>135888587</v>
       </c>
       <c r="B124" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>135889674</v>
       </c>
       <c r="B125" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>135945077</v>
       </c>
       <c r="B126" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>135888848</v>
       </c>
       <c r="B127" t="n">
-        <v>99316</v>
+        <v>99329</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>135888822</v>
       </c>
       <c r="B128" t="n">
-        <v>99338</v>
+        <v>99351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>135944179</v>
       </c>
       <c r="B129" t="n">
-        <v>108339</v>
+        <v>108352</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>135888619</v>
       </c>
       <c r="B130" t="n">
-        <v>99218</v>
+        <v>99231</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>135889613</v>
       </c>
       <c r="B131" t="n">
-        <v>99218</v>
+        <v>99231</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>135889209</v>
       </c>
       <c r="B132" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>135944165</v>
       </c>
       <c r="B133" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>135889164</v>
       </c>
       <c r="B134" t="n">
-        <v>106440</v>
+        <v>106453</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>135944158</v>
       </c>
       <c r="B135" t="n">
-        <v>106440</v>
+        <v>106453</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>135944178</v>
       </c>
       <c r="B136" t="n">
-        <v>106440</v>
+        <v>106453</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>135944184</v>
       </c>
       <c r="B137" t="n">
-        <v>106440</v>
+        <v>106453</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>135888627</v>
       </c>
       <c r="B141" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>135889141</v>
       </c>
       <c r="B142" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>135889396</v>
       </c>
       <c r="B143" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>135890358</v>
       </c>
       <c r="B144" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>135917602</v>
       </c>
       <c r="B145" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>135944160</v>
       </c>
       <c r="B146" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>135944191</v>
       </c>
       <c r="B147" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>135944195</v>
       </c>
       <c r="B148" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>135888967</v>
       </c>
       <c r="B149" t="n">
-        <v>99591</v>
+        <v>99604</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>135889868</v>
       </c>
       <c r="B150" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>135944198</v>
       </c>
       <c r="B151" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>135889874</v>
       </c>
       <c r="B152" t="n">
-        <v>98365</v>
+        <v>98378</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135944188</v>
       </c>
       <c r="B153" t="n">
-        <v>101414</v>
+        <v>101427</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 31237-2026 artfynd.xlsx
+++ b/artfynd/A 31237-2026 artfynd.xlsx
@@ -11061,7 +11061,7 @@
         <v>476761</v>
       </c>
       <c r="R98" t="n">
-        <v>7044604</v>
+        <v>7044603</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -14859,7 +14859,7 @@
         <v>476761</v>
       </c>
       <c r="R130" t="n">
-        <v>7044604</v>
+        <v>7044603</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -16066,7 +16066,7 @@
         <v>476761</v>
       </c>
       <c r="R141" t="n">
-        <v>7044604</v>
+        <v>7044603</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>

--- a/artfynd/A 31237-2026 artfynd.xlsx
+++ b/artfynd/A 31237-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890448</v>
       </c>
       <c r="B2" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135944192</v>
       </c>
       <c r="B3" t="n">
-        <v>89453</v>
+        <v>89454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135890254</v>
       </c>
       <c r="B4" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917629</v>
       </c>
       <c r="B5" t="n">
-        <v>92660</v>
+        <v>92661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135888100</v>
       </c>
       <c r="B6" t="n">
-        <v>92083</v>
+        <v>92084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917622</v>
       </c>
       <c r="B7" t="n">
-        <v>92083</v>
+        <v>92084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135888945</v>
       </c>
       <c r="B9" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135889310</v>
       </c>
       <c r="B10" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135890261</v>
       </c>
       <c r="B11" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>135890410</v>
       </c>
       <c r="B12" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135890469</v>
       </c>
       <c r="B13" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135917603</v>
       </c>
       <c r="B14" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135917607</v>
       </c>
       <c r="B15" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135945068</v>
       </c>
       <c r="B16" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135945090</v>
       </c>
       <c r="B17" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>135890793</v>
       </c>
       <c r="B23" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>135889516</v>
       </c>
       <c r="B31" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>135944174</v>
       </c>
       <c r="B32" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>135917605</v>
       </c>
       <c r="B33" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>135944194</v>
       </c>
       <c r="B34" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>135887935</v>
       </c>
       <c r="B35" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>135917600</v>
       </c>
       <c r="B36" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135917609</v>
       </c>
       <c r="B37" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>135917632</v>
       </c>
       <c r="B38" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>135944171</v>
       </c>
       <c r="B39" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135944197</v>
       </c>
       <c r="B40" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>135945066</v>
       </c>
       <c r="B41" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>135945067</v>
       </c>
       <c r="B42" t="n">
-        <v>89317</v>
+        <v>89318</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135887747</v>
       </c>
       <c r="B43" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>135890276</v>
       </c>
       <c r="B44" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135944200</v>
       </c>
       <c r="B45" t="n">
-        <v>92050</v>
+        <v>92051</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>476761</v>
       </c>
       <c r="R98" t="n">
-        <v>7044603</v>
+        <v>7044604</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -14493,7 +14493,7 @@
         <v>135888848</v>
       </c>
       <c r="B127" t="n">
-        <v>99329</v>
+        <v>99330</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>135888822</v>
       </c>
       <c r="B128" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>135944179</v>
       </c>
       <c r="B129" t="n">
-        <v>108352</v>
+        <v>108353</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>135888619</v>
       </c>
       <c r="B130" t="n">
-        <v>99231</v>
+        <v>99232</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>476761</v>
       </c>
       <c r="R130" t="n">
-        <v>7044603</v>
+        <v>7044604</v>
       </c>
       <c r="S130" t="n">
         <v>20</v>
@@ -14936,7 +14936,7 @@
         <v>135889613</v>
       </c>
       <c r="B131" t="n">
-        <v>99231</v>
+        <v>99232</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>135889209</v>
       </c>
       <c r="B132" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>135944165</v>
       </c>
       <c r="B133" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>135889164</v>
       </c>
       <c r="B134" t="n">
-        <v>106453</v>
+        <v>106454</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>135944158</v>
       </c>
       <c r="B135" t="n">
-        <v>106453</v>
+        <v>106454</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>135944178</v>
       </c>
       <c r="B136" t="n">
-        <v>106453</v>
+        <v>106454</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>135944184</v>
       </c>
       <c r="B137" t="n">
-        <v>106453</v>
+        <v>106454</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>135888627</v>
       </c>
       <c r="B141" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>476761</v>
       </c>
       <c r="R141" t="n">
-        <v>7044603</v>
+        <v>7044604</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16143,7 +16143,7 @@
         <v>135889141</v>
       </c>
       <c r="B142" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>135889396</v>
       </c>
       <c r="B143" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>135890358</v>
       </c>
       <c r="B144" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>135917602</v>
       </c>
       <c r="B145" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>135944160</v>
       </c>
       <c r="B146" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>135944191</v>
       </c>
       <c r="B147" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>135944195</v>
       </c>
       <c r="B148" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>135888967</v>
       </c>
       <c r="B149" t="n">
-        <v>99604</v>
+        <v>99605</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>135889868</v>
       </c>
       <c r="B150" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>135944198</v>
       </c>
       <c r="B151" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>135889874</v>
       </c>
       <c r="B152" t="n">
-        <v>98378</v>
+        <v>98379</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135944188</v>
       </c>
       <c r="B153" t="n">
-        <v>101427</v>
+        <v>101428</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 31237-2026 artfynd.xlsx
+++ b/artfynd/A 31237-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890448</v>
       </c>
       <c r="B2" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135944192</v>
       </c>
       <c r="B3" t="n">
-        <v>89454</v>
+        <v>89467</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135890254</v>
       </c>
       <c r="B4" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917629</v>
       </c>
       <c r="B5" t="n">
-        <v>92661</v>
+        <v>92674</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135888100</v>
       </c>
       <c r="B6" t="n">
-        <v>92084</v>
+        <v>92097</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917622</v>
       </c>
       <c r="B7" t="n">
-        <v>92084</v>
+        <v>92097</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135888945</v>
       </c>
       <c r="B9" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135889310</v>
       </c>
       <c r="B10" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135890261</v>
       </c>
       <c r="B11" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>135890410</v>
       </c>
       <c r="B12" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135890469</v>
       </c>
       <c r="B13" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135917603</v>
       </c>
       <c r="B14" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135917607</v>
       </c>
       <c r="B15" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135945068</v>
       </c>
       <c r="B16" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135945090</v>
       </c>
       <c r="B17" t="n">
-        <v>92102</v>
+        <v>92115</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>135890793</v>
       </c>
       <c r="B23" t="n">
-        <v>92430</v>
+        <v>92443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135917639</v>
       </c>
       <c r="B24" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>135944181</v>
       </c>
       <c r="B25" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>135945080</v>
       </c>
       <c r="B26" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>135945081</v>
       </c>
       <c r="B27" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>135945082</v>
       </c>
       <c r="B28" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>135945083</v>
       </c>
       <c r="B29" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>135945084</v>
       </c>
       <c r="B30" t="n">
-        <v>80576</v>
+        <v>80589</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>135889516</v>
       </c>
       <c r="B31" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>135944174</v>
       </c>
       <c r="B32" t="n">
-        <v>96540</v>
+        <v>96553</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>135917605</v>
       </c>
       <c r="B33" t="n">
-        <v>92313</v>
+        <v>92326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>135944194</v>
       </c>
       <c r="B34" t="n">
-        <v>92313</v>
+        <v>92326</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>135887935</v>
       </c>
       <c r="B35" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>135917600</v>
       </c>
       <c r="B36" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135917609</v>
       </c>
       <c r="B37" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>135917632</v>
       </c>
       <c r="B38" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>135944171</v>
       </c>
       <c r="B39" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135944197</v>
       </c>
       <c r="B40" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>135945066</v>
       </c>
       <c r="B41" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>135945067</v>
       </c>
       <c r="B42" t="n">
-        <v>89318</v>
+        <v>89331</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135887747</v>
       </c>
       <c r="B43" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>135890276</v>
       </c>
       <c r="B44" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135944200</v>
       </c>
       <c r="B45" t="n">
-        <v>92051</v>
+        <v>92064</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>135887305</v>
       </c>
       <c r="B48" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>135888884</v>
       </c>
       <c r="B49" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>135889085</v>
       </c>
       <c r="B50" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>135889333</v>
       </c>
       <c r="B51" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135917634</v>
       </c>
       <c r="B52" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135917649</v>
       </c>
       <c r="B53" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>135917650</v>
       </c>
       <c r="B54" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>135917651</v>
       </c>
       <c r="B55" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>135917653</v>
       </c>
       <c r="B56" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>135917655</v>
       </c>
       <c r="B57" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>135917663</v>
       </c>
       <c r="B58" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>135917664</v>
       </c>
       <c r="B59" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>135917666</v>
       </c>
       <c r="B60" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>135944159</v>
       </c>
       <c r="B61" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>135944161</v>
       </c>
       <c r="B62" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>135944164</v>
       </c>
       <c r="B63" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>135944167</v>
       </c>
       <c r="B64" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>135944170</v>
       </c>
       <c r="B65" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>135944172</v>
       </c>
       <c r="B66" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>135944187</v>
       </c>
       <c r="B67" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>135944189</v>
       </c>
       <c r="B68" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>135944190</v>
       </c>
       <c r="B69" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>135944196</v>
       </c>
       <c r="B70" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>135944199</v>
       </c>
       <c r="B71" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>135944202</v>
       </c>
       <c r="B72" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>135945091</v>
       </c>
       <c r="B73" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135945092</v>
       </c>
       <c r="B74" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>135888499</v>
       </c>
       <c r="B75" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>135888120</v>
       </c>
       <c r="B76" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>135917620</v>
       </c>
       <c r="B77" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>135917631</v>
       </c>
       <c r="B78" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>135945085</v>
       </c>
       <c r="B79" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>135945086</v>
       </c>
       <c r="B80" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>135945087</v>
       </c>
       <c r="B81" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>135945088</v>
       </c>
       <c r="B82" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>135945089</v>
       </c>
       <c r="B83" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>135945094</v>
       </c>
       <c r="B84" t="n">
-        <v>79716</v>
+        <v>79729</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>135888337</v>
       </c>
       <c r="B86" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>135888567</v>
       </c>
       <c r="B87" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>135889256</v>
       </c>
       <c r="B88" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>135890496</v>
       </c>
       <c r="B89" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>135917621</v>
       </c>
       <c r="B90" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>135888326</v>
       </c>
       <c r="B91" t="n">
-        <v>80586</v>
+        <v>80599</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>135945093</v>
       </c>
       <c r="B92" t="n">
-        <v>80586</v>
+        <v>80599</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>135888134</v>
       </c>
       <c r="B93" t="n">
-        <v>80587</v>
+        <v>80600</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>135944177</v>
       </c>
       <c r="B94" t="n">
-        <v>80587</v>
+        <v>80600</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>135888984</v>
       </c>
       <c r="B95" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>135944169</v>
       </c>
       <c r="B96" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10899,7 +10899,7 @@
         <v>135888059</v>
       </c>
       <c r="B97" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>135888595</v>
       </c>
       <c r="B98" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>135888744</v>
       </c>
       <c r="B99" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>135888896</v>
       </c>
       <c r="B100" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>135889188</v>
       </c>
       <c r="B101" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>135889243</v>
       </c>
       <c r="B102" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>135889343</v>
       </c>
       <c r="B103" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>135890314</v>
       </c>
       <c r="B104" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>135917612</v>
       </c>
       <c r="B105" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>135917618</v>
       </c>
       <c r="B106" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>135917637</v>
       </c>
       <c r="B107" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>135917656</v>
       </c>
       <c r="B108" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12383,7 +12383,7 @@
         <v>135917657</v>
       </c>
       <c r="B109" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>135917659</v>
       </c>
       <c r="B110" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12627,7 +12627,7 @@
         <v>135917661</v>
       </c>
       <c r="B111" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12749,7 +12749,7 @@
         <v>135917668</v>
       </c>
       <c r="B112" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12871,7 +12871,7 @@
         <v>135917669</v>
       </c>
       <c r="B113" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12993,7 +12993,7 @@
         <v>135944193</v>
       </c>
       <c r="B114" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         <v>135945069</v>
       </c>
       <c r="B115" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>135945070</v>
       </c>
       <c r="B116" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>135945071</v>
       </c>
       <c r="B117" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>135945072</v>
       </c>
       <c r="B118" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13560,7 +13560,7 @@
         <v>135945073</v>
       </c>
       <c r="B119" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13675,7 +13675,7 @@
         <v>135945074</v>
       </c>
       <c r="B120" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13790,7 +13790,7 @@
         <v>135945075</v>
       </c>
       <c r="B121" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>135945076</v>
       </c>
       <c r="B122" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>135917641</v>
       </c>
       <c r="B123" t="n">
-        <v>57171</v>
+        <v>57184</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>135888587</v>
       </c>
       <c r="B124" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>135889674</v>
       </c>
       <c r="B125" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14379,7 +14379,7 @@
         <v>135945077</v>
       </c>
       <c r="B126" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>135888848</v>
       </c>
       <c r="B127" t="n">
-        <v>99330</v>
+        <v>99343</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>135888822</v>
       </c>
       <c r="B128" t="n">
-        <v>99352</v>
+        <v>99365</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>135944179</v>
       </c>
       <c r="B129" t="n">
-        <v>108353</v>
+        <v>108366</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>135888619</v>
       </c>
       <c r="B130" t="n">
-        <v>99232</v>
+        <v>99245</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>135889613</v>
       </c>
       <c r="B131" t="n">
-        <v>99232</v>
+        <v>99245</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>135889209</v>
       </c>
       <c r="B132" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>135944165</v>
       </c>
       <c r="B133" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>135889164</v>
       </c>
       <c r="B134" t="n">
-        <v>106454</v>
+        <v>106467</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>135944158</v>
       </c>
       <c r="B135" t="n">
-        <v>106454</v>
+        <v>106467</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>135944178</v>
       </c>
       <c r="B136" t="n">
-        <v>106454</v>
+        <v>106467</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>135944184</v>
       </c>
       <c r="B137" t="n">
-        <v>106454</v>
+        <v>106467</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>135888627</v>
       </c>
       <c r="B141" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>135889141</v>
       </c>
       <c r="B142" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>135889396</v>
       </c>
       <c r="B143" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>135890358</v>
       </c>
       <c r="B144" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>135917602</v>
       </c>
       <c r="B145" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>135944160</v>
       </c>
       <c r="B146" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>135944191</v>
       </c>
       <c r="B147" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>135944195</v>
       </c>
       <c r="B148" t="n">
-        <v>99350</v>
+        <v>99363</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>135888967</v>
       </c>
       <c r="B149" t="n">
-        <v>99605</v>
+        <v>99618</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>135889868</v>
       </c>
       <c r="B150" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>135944198</v>
       </c>
       <c r="B151" t="n">
-        <v>99134</v>
+        <v>99147</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>135889874</v>
       </c>
       <c r="B152" t="n">
-        <v>98379</v>
+        <v>98392</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135944188</v>
       </c>
       <c r="B153" t="n">
-        <v>101428</v>
+        <v>101441</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/A 31237-2026 artfynd.xlsx
+++ b/artfynd/A 31237-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135890448</v>
       </c>
       <c r="B2" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135944192</v>
       </c>
       <c r="B3" t="n">
-        <v>89467</v>
+        <v>89468</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135890254</v>
       </c>
       <c r="B4" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135917629</v>
       </c>
       <c r="B5" t="n">
-        <v>92674</v>
+        <v>92675</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135888100</v>
       </c>
       <c r="B6" t="n">
-        <v>92097</v>
+        <v>92098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>135917622</v>
       </c>
       <c r="B7" t="n">
-        <v>92097</v>
+        <v>92098</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>135888945</v>
       </c>
       <c r="B9" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>135889310</v>
       </c>
       <c r="B10" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>135890261</v>
       </c>
       <c r="B11" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>135890410</v>
       </c>
       <c r="B12" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>135890469</v>
       </c>
       <c r="B13" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>135917603</v>
       </c>
       <c r="B14" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>135917607</v>
       </c>
       <c r="B15" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>135945068</v>
       </c>
       <c r="B16" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,7 +2333,7 @@
         <v>135945090</v>
       </c>
       <c r="B17" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2946,7 +2946,7 @@
         <v>135890793</v>
       </c>
       <c r="B23" t="n">
-        <v>92443</v>
+        <v>92444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         <v>135917639</v>
       </c>
       <c r="B24" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,7 +3170,7 @@
         <v>135944181</v>
       </c>
       <c r="B25" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>135945080</v>
       </c>
       <c r="B26" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>135945081</v>
       </c>
       <c r="B27" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>135945082</v>
       </c>
       <c r="B28" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>135945083</v>
       </c>
       <c r="B29" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>135945084</v>
       </c>
       <c r="B30" t="n">
-        <v>80589</v>
+        <v>80590</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>135889516</v>
       </c>
       <c r="B31" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>135944174</v>
       </c>
       <c r="B32" t="n">
-        <v>96553</v>
+        <v>96554</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>135917605</v>
       </c>
       <c r="B33" t="n">
-        <v>92326</v>
+        <v>92327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>135944194</v>
       </c>
       <c r="B34" t="n">
-        <v>92326</v>
+        <v>92327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>135887935</v>
       </c>
       <c r="B35" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>135917600</v>
       </c>
       <c r="B36" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>135917609</v>
       </c>
       <c r="B37" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>135917632</v>
       </c>
       <c r="B38" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>135944171</v>
       </c>
       <c r="B39" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4760,7 +4760,7 @@
         <v>135944197</v>
       </c>
       <c r="B40" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>135945066</v>
       </c>
       <c r="B41" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4964,7 +4964,7 @@
         <v>135945067</v>
       </c>
       <c r="B42" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>135887747</v>
       </c>
       <c r="B43" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>135890276</v>
       </c>
       <c r="B44" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>135944200</v>
       </c>
       <c r="B45" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
         <v>135887305</v>
       </c>
       <c r="B48" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         <v>135888884</v>
       </c>
       <c r="B49" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>135889085</v>
       </c>
       <c r="B50" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>135889333</v>
       </c>
       <c r="B51" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>135917634</v>
       </c>
       <c r="B52" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>135917649</v>
       </c>
       <c r="B53" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
         <v>135917650</v>
       </c>
       <c r="B54" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6385,7 +6385,7 @@
         <v>135917651</v>
       </c>
       <c r="B55" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>135917653</v>
       </c>
       <c r="B56" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>135917655</v>
       </c>
       <c r="B57" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6736,7 +6736,7 @@
         <v>135917663</v>
       </c>
       <c r="B58" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>135917664</v>
       </c>
       <c r="B59" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>135917666</v>
       </c>
       <c r="B60" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         <v>135944159</v>
       </c>
       <c r="B61" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>135944161</v>
       </c>
       <c r="B62" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         <v>135944164</v>
       </c>
       <c r="B63" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         <v>135944167</v>
       </c>
       <c r="B64" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>135944170</v>
       </c>
       <c r="B65" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>135944172</v>
       </c>
       <c r="B66" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7699,7 +7699,7 @@
         <v>135944187</v>
       </c>
       <c r="B67" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>135944189</v>
       </c>
       <c r="B68" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>135944190</v>
       </c>
       <c r="B69" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>135944196</v>
       </c>
       <c r="B70" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>135944199</v>
       </c>
       <c r="B71" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>135944202</v>
       </c>
       <c r="B72" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>135945091</v>
       </c>
       <c r="B73" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         <v>135945092</v>
       </c>
       <c r="B74" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8515,7 +8515,7 @@
         <v>135888499</v>
       </c>
       <c r="B75" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>135888120</v>
       </c>
       <c r="B76" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>135917620</v>
       </c>
       <c r="B77" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>135917631</v>
       </c>
       <c r="B78" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8968,7 +8968,7 @@
         <v>135945085</v>
       </c>
       <c r="B79" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9070,7 +9070,7 @@
         <v>135945086</v>
       </c>
       <c r="B80" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>135945087</v>
       </c>
       <c r="B81" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9274,7 +9274,7 @@
         <v>135945088</v>
       </c>
       <c r="B82" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>135945089</v>
       </c>
       <c r="B83" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>135945094</v>
       </c>
       <c r="B84" t="n">
-        <v>79729</v>
+        <v>79730</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>135888337</v>
       </c>
       <c r="B86" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9794,7 +9794,7 @@
         <v>135888567</v>
       </c>
       <c r="B87" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>135889256</v>
       </c>
       <c r="B88" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>135890496</v>
       </c>
       <c r="B89" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
         <v>135917621</v>
       </c>
       <c r="B90" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10242,7 +10242,7 @@
         <v>135888326</v>
       </c>
       <c r="B91" t="n">
-        <v>80599</v>
+        <v>80600</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>135945093</v>
       </c>
       <c r="B92" t="n">
-        <v>80599</v>
+        <v>80600</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10456,7 +10456,7 @@
         <v>135888134</v>
       </c>
       <c r="B93" t="n">
-        <v>80600</v>
+        <v>80601</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>135944177</v>
       </c>
       <c r="B94" t="n">
-        <v>80600</v>
+        <v>80601</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>135888848</v>
       </c>
       <c r="B127" t="n">
-        <v>99343</v>
+        <v>99344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>135888822</v>
       </c>
       <c r="B128" t="n">
-        <v>99365</v>
+        <v>99366</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14717,7 +14717,7 @@
         <v>135944179</v>
       </c>
       <c r="B129" t="n">
-        <v>108366</v>
+        <v>108367</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14819,7 +14819,7 @@
         <v>135888619</v>
       </c>
       <c r="B130" t="n">
-        <v>99245</v>
+        <v>99246</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>135889613</v>
       </c>
       <c r="B131" t="n">
-        <v>99245</v>
+        <v>99246</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>135889209</v>
       </c>
       <c r="B132" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>135944165</v>
       </c>
       <c r="B133" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15293,7 +15293,7 @@
         <v>135889164</v>
       </c>
       <c r="B134" t="n">
-        <v>106467</v>
+        <v>106468</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>135944158</v>
       </c>
       <c r="B135" t="n">
-        <v>106467</v>
+        <v>106468</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>135944178</v>
       </c>
       <c r="B136" t="n">
-        <v>106467</v>
+        <v>106468</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>135944184</v>
       </c>
       <c r="B137" t="n">
-        <v>106467</v>
+        <v>106468</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>135888627</v>
       </c>
       <c r="B141" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>135889141</v>
       </c>
       <c r="B142" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>135889396</v>
       </c>
       <c r="B143" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>135890358</v>
       </c>
       <c r="B144" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>135917602</v>
       </c>
       <c r="B145" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>135944160</v>
       </c>
       <c r="B146" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>135944191</v>
       </c>
       <c r="B147" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>135944195</v>
       </c>
       <c r="B148" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>135888967</v>
       </c>
       <c r="B149" t="n">
-        <v>99618</v>
+        <v>99619</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>135889868</v>
       </c>
       <c r="B150" t="n">
-        <v>99147</v>
+        <v>99148</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>135944198</v>
       </c>
       <c r="B151" t="n">
-        <v>99147</v>
+        <v>99148</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>135889874</v>
       </c>
       <c r="B152" t="n">
-        <v>98392</v>
+        <v>98393</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>135944188</v>
       </c>
       <c r="B153" t="n">
-        <v>101441</v>
+        <v>101442</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
